--- a/BOM/BOM_LCSC.xlsx
+++ b/BOM/BOM_LCSC.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="318">
   <si>
     <t>S. No.</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>CR1206FR050P05R</t>
-  </si>
-  <si>
-    <t>0.05R</t>
   </si>
   <si>
     <t>100K</t>
@@ -251,16 +248,6 @@
     <t xml:space="preserve">TDK </t>
   </si>
   <si>
-    <t xml:space="preserve">CAP CER 0.1UF 25V X5R 0402
-</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>0402X104K250CT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Walsin </t>
   </si>
   <si>
@@ -314,9 +301,6 @@
     <t>FN18N220J500PSG</t>
   </si>
   <si>
-    <t>40V 3A 550mV @ 3A SMA Schottky Barrier Diodes (SBD) RoHS</t>
-  </si>
-  <si>
     <t>D1, D9, D10</t>
   </si>
   <si>
@@ -482,12 +466,6 @@
   </si>
   <si>
     <t>1206</t>
-  </si>
-  <si>
-    <t>Thick Film Resistor - 1Kohm, 1%, 0603</t>
-  </si>
-  <si>
-    <t>WR06X102 JTL</t>
   </si>
   <si>
     <t>Thick Film Resistor -  12Kohm, 1%, 0603</t>
@@ -836,9 +814,6 @@
     <t>100pF</t>
   </si>
   <si>
-    <t>C237172</t>
-  </si>
-  <si>
     <t>C122324</t>
   </si>
   <si>
@@ -897,9 +872,6 @@
   </si>
   <si>
     <t>C500612</t>
-  </si>
-  <si>
-    <t>0.001ohm</t>
   </si>
   <si>
     <t>C115325</t>
@@ -944,6 +916,144 @@
   <si>
     <t>C1,C10</t>
   </si>
+  <si>
+    <t xml:space="preserve">DIODE SCHOTTKY 40V 3A SMC
+</t>
+  </si>
+  <si>
+    <t>C217683</t>
+  </si>
+  <si>
+    <t>ARG03FTC1000</t>
+  </si>
+  <si>
+    <t>C465460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-03JA7----0R
+</t>
+  </si>
+  <si>
+    <t>C304686</t>
+  </si>
+  <si>
+    <t>0.001Ω</t>
+  </si>
+  <si>
+    <t>100Ω</t>
+  </si>
+  <si>
+    <t>0.05Ω</t>
+  </si>
+  <si>
+    <t>0Ω</t>
+  </si>
+  <si>
+    <t>10Ω</t>
+  </si>
+  <si>
+    <t>C103210</t>
+  </si>
+  <si>
+    <t>RTT03103JTP</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>C403211</t>
+  </si>
+  <si>
+    <t>ERJ3EKF4122V</t>
+  </si>
+  <si>
+    <t>41.2K</t>
+  </si>
+  <si>
+    <t>C118393</t>
+  </si>
+  <si>
+    <t>3.3K</t>
+  </si>
+  <si>
+    <t>C149672</t>
+  </si>
+  <si>
+    <t>0.1Ω</t>
+  </si>
+  <si>
+    <t>C706413</t>
+  </si>
+  <si>
+    <t>400Ω</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAKRO </t>
+  </si>
+  <si>
+    <t>C620330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPSALPINE </t>
+  </si>
+  <si>
+    <t>C125034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUOLOP </t>
+  </si>
+  <si>
+    <t>C351410</t>
+  </si>
+  <si>
+    <t>TOPPOWER</t>
+  </si>
+  <si>
+    <t>C51699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortune </t>
+  </si>
+  <si>
+    <t>C16052</t>
+  </si>
+  <si>
+    <t>C14877</t>
+  </si>
+  <si>
+    <t>WinSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunrom </t>
+  </si>
+  <si>
+    <t>Sunrom</t>
+  </si>
+  <si>
+    <t>Winsource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XFCN </t>
+  </si>
+  <si>
+    <t>C492420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS-03K1001FT
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R8,wala part b same ha is lye merge kr dia 1 part no me </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10,wala part b same ha is lye merge kr dia 1 part no me </t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Chipmall</t>
+  </si>
 </sst>
 </file>
 
@@ -953,7 +1063,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00000"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00000"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -1082,7 +1192,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1113,14 +1223,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="24">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1328,21 +1432,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -1362,30 +1451,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1412,6 +1477,41 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1423,12 +1523,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1572,13 +1707,13 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1657,27 +1792,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1723,27 +1837,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1793,13 +1898,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1808,9 +1910,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1823,7 +1922,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1838,9 +1937,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1850,44 +1946,43 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1896,9 +1991,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1908,9 +2000,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1923,76 +2012,126 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2274,7 +2413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE61"/>
+  <dimension ref="A1:AE59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="40" bestFit="1" customWidth="1"/>
@@ -2309,37 +2448,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="82"/>
+      <c r="A1" s="175" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="176"/>
+      <c r="Q1" s="176"/>
+      <c r="R1" s="176"/>
+      <c r="S1" s="176"/>
+      <c r="T1" s="176"/>
+      <c r="U1" s="176"/>
+      <c r="V1" s="176"/>
+      <c r="W1" s="176"/>
+      <c r="X1" s="176"/>
+      <c r="Y1" s="176"/>
+      <c r="Z1" s="176"/>
+      <c r="AA1" s="176"/>
+      <c r="AB1" s="176"/>
+      <c r="AC1" s="177"/>
     </row>
     <row r="2" spans="1:31" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
@@ -2379,52 +2518,52 @@
         <v>11</v>
       </c>
       <c r="M2" s="54" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="N2" s="54" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="O2" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="P2" s="54" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q2" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="R2" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="T2" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="U2" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="P2" s="54" t="s">
+      <c r="V2" s="51" t="s">
         <v>230</v>
       </c>
-      <c r="Q2" s="54" t="s">
+      <c r="W2" s="50" t="s">
         <v>231</v>
       </c>
-      <c r="R2" s="55" t="s">
-        <v>47</v>
-      </c>
-      <c r="S2" s="50" t="s">
+      <c r="X2" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="T2" s="50" t="s">
+      <c r="Y2" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="U2" s="50" t="s">
+      <c r="Z2" s="51" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA2" s="50" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB2" s="51" t="s">
         <v>236</v>
-      </c>
-      <c r="V2" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="W2" s="50" t="s">
-        <v>238</v>
-      </c>
-      <c r="X2" s="51" t="s">
-        <v>239</v>
-      </c>
-      <c r="Y2" s="50" t="s">
-        <v>240</v>
-      </c>
-      <c r="Z2" s="51" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA2" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="AB2" s="51" t="s">
-        <v>243</v>
       </c>
       <c r="AC2" s="54" t="s">
         <v>12</v>
@@ -2434,29 +2573,29 @@
       <c r="A3" s="52">
         <v>1</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="81" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="88" t="s">
-        <v>281</v>
-      </c>
-      <c r="E3" s="89" t="s">
+      <c r="F3" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="G3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="H3" s="76" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I3" s="74" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>14</v>
@@ -2464,7 +2603,7 @@
       <c r="K3" s="4">
         <v>50</v>
       </c>
-      <c r="L3" s="127">
+      <c r="L3" s="117">
         <v>1</v>
       </c>
       <c r="M3" s="4">
@@ -2482,7 +2621,7 @@
       <c r="Q3" s="4">
         <v>10500</v>
       </c>
-      <c r="R3" s="138" t="s">
+      <c r="R3" s="126" t="s">
         <v>15</v>
       </c>
       <c r="S3" s="56">
@@ -2520,7 +2659,9 @@
         <f>AA3*Q3</f>
         <v>47.249999999999993</v>
       </c>
-      <c r="AC3" s="7"/>
+      <c r="AC3" s="185" t="s">
+        <v>315</v>
+      </c>
       <c r="AD3" s="8"/>
       <c r="AE3" s="8"/>
     </row>
@@ -2528,30 +2669,30 @@
       <c r="A4" s="52">
         <v>2</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="90" t="s">
+      <c r="B4" s="168"/>
+      <c r="C4" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="91" t="s">
+      <c r="E4" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="92" t="s">
+      <c r="F4" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="G4" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>57</v>
-      </c>
       <c r="H4" s="66" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="I4" s="66" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="K4" s="11">
         <v>50</v>
@@ -2559,22 +2700,22 @@
       <c r="L4" s="11">
         <v>21</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="11">
         <v>250</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="11">
         <v>500</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="11">
         <v>11000</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="11">
         <v>22000</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="11">
         <v>220000</v>
       </c>
-      <c r="R4" s="139" t="s">
+      <c r="R4" s="127" t="s">
         <v>15</v>
       </c>
       <c r="S4" s="57">
@@ -2594,22 +2735,22 @@
       <c r="W4" s="13">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="X4" s="6">
-        <f t="shared" ref="X4:X52" si="0">W4*O4</f>
+      <c r="X4" s="13">
+        <f t="shared" ref="X4:X50" si="0">W4*O4</f>
         <v>46.199999999999996</v>
       </c>
       <c r="Y4" s="13">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="Z4" s="6">
-        <f t="shared" ref="Z4:Z52" si="1">Y4*P4</f>
+      <c r="Z4" s="13">
+        <f t="shared" ref="Z4:Z50" si="1">Y4*P4</f>
         <v>92.399999999999991</v>
       </c>
       <c r="AA4" s="13">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="AB4" s="6">
-        <f t="shared" ref="AB4:AB52" si="2">AA4*Q4</f>
+      <c r="AB4" s="13">
+        <f t="shared" ref="AB4:AB50" si="2">AA4*Q4</f>
         <v>880</v>
       </c>
       <c r="AC4" s="14"/>
@@ -2620,27 +2761,27 @@
       <c r="A5" s="52">
         <v>3</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="93" t="s">
+      <c r="B5" s="168"/>
+      <c r="C5" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="94" t="s">
+      <c r="E5" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="F5" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="G5" s="9" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="H5" s="66" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="I5" s="67" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>17</v>
@@ -2648,59 +2789,59 @@
       <c r="K5" s="11">
         <v>20</v>
       </c>
-      <c r="L5" s="128">
+      <c r="L5" s="118">
         <v>5</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="11">
         <v>60</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5" s="11">
         <v>120</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="11">
         <v>2650</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="11">
         <v>5300</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="11">
         <v>52000</v>
       </c>
-      <c r="R5" s="139" t="s">
+      <c r="R5" s="127" t="s">
         <v>15</v>
       </c>
       <c r="S5" s="57">
         <v>3.1800000000000002E-2</v>
       </c>
       <c r="T5" s="13">
-        <f t="shared" ref="T5:T52" si="3">S5*M5</f>
+        <f t="shared" ref="T5:T50" si="3">S5*M5</f>
         <v>1.9080000000000001</v>
       </c>
       <c r="U5" s="57">
         <v>3.1800000000000002E-2</v>
       </c>
       <c r="V5" s="13">
-        <f t="shared" ref="V5:V52" si="4">U5*N5</f>
+        <f t="shared" ref="V5:V50" si="4">U5*N5</f>
         <v>3.8160000000000003</v>
       </c>
       <c r="W5" s="13">
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="X5" s="6">
+      <c r="X5" s="13">
         <f t="shared" si="0"/>
         <v>52.470000000000006</v>
       </c>
       <c r="Y5" s="13">
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="Z5" s="6">
+      <c r="Z5" s="13">
         <f t="shared" si="1"/>
         <v>104.94000000000001</v>
       </c>
       <c r="AA5" s="13">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="AB5" s="6">
+      <c r="AB5" s="13">
         <f t="shared" si="2"/>
         <v>977.6</v>
       </c>
@@ -2712,27 +2853,27 @@
       <c r="A6" s="52">
         <v>4</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="93" t="s">
+      <c r="B6" s="168"/>
+      <c r="C6" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="94" t="s">
+      <c r="E6" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="F6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>65</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="H6" s="66" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>18</v>
@@ -2740,35 +2881,35 @@
       <c r="K6" s="11">
         <v>5</v>
       </c>
-      <c r="L6" s="128">
+      <c r="L6" s="118">
         <v>2</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="11">
         <v>25</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="11">
         <v>45</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="11">
         <v>1050</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="11">
         <v>2100</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="11">
         <v>21000</v>
       </c>
-      <c r="R6" s="183" t="s">
+      <c r="R6" s="159" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="140">
+      <c r="S6" s="128">
         <v>0.1075</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="3"/>
         <v>2.6875</v>
       </c>
-      <c r="U6" s="140">
+      <c r="U6" s="128">
         <v>0.1075</v>
       </c>
       <c r="V6" s="13">
@@ -2778,21 +2919,21 @@
       <c r="W6" s="13">
         <v>7.6700000000000004E-2</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6" s="13">
         <f t="shared" si="0"/>
         <v>80.535000000000011</v>
       </c>
       <c r="Y6" s="13">
         <v>7.6700000000000004E-2</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="Z6" s="13">
         <f t="shared" si="1"/>
         <v>161.07000000000002</v>
       </c>
       <c r="AA6" s="13">
         <v>7.3899999999999993E-2</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AB6" s="13">
         <f t="shared" si="2"/>
         <v>1551.8999999999999</v>
       </c>
@@ -2804,53 +2945,53 @@
       <c r="A7" s="52">
         <v>5</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="93" t="s">
+      <c r="B7" s="168"/>
+      <c r="C7" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="94" t="s">
+      <c r="E7" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="16" t="s">
+      <c r="G7" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="H7" s="66" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="I7" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="J7" s="15" t="s">
         <v>245</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>252</v>
       </c>
       <c r="K7" s="68">
         <v>50</v>
       </c>
-      <c r="L7" s="128">
+      <c r="L7" s="118">
         <v>1</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="11">
         <v>50</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="11">
         <v>50</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="11">
         <v>550</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="11">
         <v>1050</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="Q7" s="11">
         <v>10500</v>
       </c>
-      <c r="R7" s="183" t="s">
+      <c r="R7" s="159" t="s">
         <v>15</v>
       </c>
       <c r="S7" s="69">
@@ -2870,21 +3011,21 @@
       <c r="W7" s="70">
         <v>1.21E-2</v>
       </c>
-      <c r="X7" s="6">
+      <c r="X7" s="13">
         <f t="shared" si="0"/>
         <v>6.6549999999999994</v>
       </c>
       <c r="Y7" s="70">
         <v>1.21E-2</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="Z7" s="13">
         <f t="shared" si="1"/>
         <v>12.705</v>
       </c>
       <c r="AA7" s="70">
         <v>1.0200000000000001E-2</v>
       </c>
-      <c r="AB7" s="6">
+      <c r="AB7" s="13">
         <f t="shared" si="2"/>
         <v>107.10000000000001</v>
       </c>
@@ -2896,89 +3037,91 @@
       <c r="A8" s="52">
         <v>6</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="196" t="s">
+      <c r="B8" s="168"/>
+      <c r="C8" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="192" t="s">
+      <c r="D8" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="192" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="193" t="s">
+      <c r="E8" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="194" t="s">
+      <c r="F8" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="195" t="s">
-        <v>253</v>
-      </c>
-      <c r="I8" s="193" t="s">
-        <v>245</v>
-      </c>
-      <c r="J8" s="194" t="s">
+      <c r="G8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="66" t="s">
         <v>246</v>
       </c>
-      <c r="K8" s="197">
-        <v>100</v>
-      </c>
-      <c r="L8" s="128">
+      <c r="I8" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="K8" s="11">
         <v>1</v>
       </c>
-      <c r="M8" s="4">
-        <v>100</v>
-      </c>
-      <c r="N8" s="4">
-        <v>100</v>
-      </c>
-      <c r="O8" s="4">
-        <v>600</v>
-      </c>
-      <c r="P8" s="4">
-        <v>1100</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>10500</v>
-      </c>
-      <c r="R8" s="183" t="s">
+      <c r="L8" s="118">
+        <v>1</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" ref="M8:M38" si="5">ROUND(L8*10*1.15,0)</f>
+        <v>12</v>
+      </c>
+      <c r="N8" s="11">
+        <f t="shared" ref="N8:N38" si="6">ROUND(L8*20*1.15,0)</f>
+        <v>23</v>
+      </c>
+      <c r="O8" s="11">
+        <v>525</v>
+      </c>
+      <c r="P8" s="11">
+        <v>1050</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>10200</v>
+      </c>
+      <c r="R8" s="159" t="s">
         <v>15</v>
       </c>
-      <c r="S8" s="57">
-        <v>2.5999999999999999E-3</v>
+      <c r="S8" s="58">
+        <v>0.76459999999999995</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="3"/>
-        <v>0.26</v>
-      </c>
-      <c r="U8" s="57">
-        <v>2.5999999999999999E-3</v>
+        <v>9.1752000000000002</v>
+      </c>
+      <c r="U8" s="58">
+        <v>0.76459999999999995</v>
       </c>
       <c r="V8" s="13">
         <f t="shared" si="4"/>
-        <v>0.26</v>
+        <v>17.585799999999999</v>
       </c>
       <c r="W8" s="13">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="X8" s="6">
+        <v>0.66549999999999998</v>
+      </c>
+      <c r="X8" s="13">
         <f t="shared" si="0"/>
-        <v>1.5599999999999998</v>
+        <v>349.38749999999999</v>
       </c>
       <c r="Y8" s="13">
-        <v>1.9E-3</v>
-      </c>
-      <c r="Z8" s="6">
+        <v>0.65639999999999998</v>
+      </c>
+      <c r="Z8" s="13">
         <f t="shared" si="1"/>
-        <v>2.09</v>
+        <v>689.22</v>
       </c>
       <c r="AA8" s="13">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="AB8" s="6">
+        <v>0.65639999999999998</v>
+      </c>
+      <c r="AB8" s="13">
         <f t="shared" si="2"/>
-        <v>16.8</v>
+        <v>6695.28</v>
       </c>
       <c r="AC8" s="14"/>
       <c r="AD8" s="8"/>
@@ -2988,93 +3131,89 @@
       <c r="A9" s="52">
         <v>7</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="93" t="s">
+      <c r="B9" s="168"/>
+      <c r="C9" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="94" t="s">
+      <c r="D9" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="92" t="s">
+      <c r="E9" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="G9" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>20</v>
-      </c>
       <c r="H9" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="I9" s="66" t="s">
-        <v>245</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="K9" s="11">
+        <v>248</v>
+      </c>
+      <c r="I9" s="77"/>
+      <c r="J9" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="K9" s="36">
+        <v>50</v>
+      </c>
+      <c r="L9" s="118">
         <v>1</v>
       </c>
-      <c r="L9" s="128">
-        <v>1</v>
-      </c>
-      <c r="M9" s="4">
-        <f t="shared" ref="M9:M40" si="5">ROUND(L9*10*1.15,0)</f>
-        <v>12</v>
-      </c>
-      <c r="N9" s="4">
-        <f t="shared" ref="N9:N40" si="6">ROUND(L9*20*1.15,0)</f>
-        <v>23</v>
-      </c>
-      <c r="O9" s="4">
-        <v>525</v>
-      </c>
-      <c r="P9" s="4">
-        <v>1050</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>10200</v>
-      </c>
-      <c r="R9" s="183" t="s">
+      <c r="M9" s="11">
+        <v>50</v>
+      </c>
+      <c r="N9" s="11">
+        <v>50</v>
+      </c>
+      <c r="O9" s="11">
+        <v>550</v>
+      </c>
+      <c r="P9" s="11">
+        <v>1100</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>10500</v>
+      </c>
+      <c r="R9" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="S9" s="58">
-        <v>0.76459999999999995</v>
+      <c r="S9" s="62">
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="T9" s="13">
         <f t="shared" si="3"/>
-        <v>9.1752000000000002</v>
-      </c>
-      <c r="U9" s="58">
-        <v>0.76459999999999995</v>
+        <v>0.245</v>
+      </c>
+      <c r="U9" s="64">
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="V9" s="13">
         <f t="shared" si="4"/>
-        <v>17.585799999999999</v>
-      </c>
-      <c r="W9" s="13">
-        <v>0.66549999999999998</v>
-      </c>
-      <c r="X9" s="6">
+        <v>0.245</v>
+      </c>
+      <c r="W9" s="63">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="X9" s="13">
         <f t="shared" si="0"/>
-        <v>349.38749999999999</v>
-      </c>
-      <c r="Y9" s="13">
-        <v>0.65639999999999998</v>
-      </c>
-      <c r="Z9" s="6">
+        <v>2.145</v>
+      </c>
+      <c r="Y9" s="63">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="Z9" s="13">
         <f t="shared" si="1"/>
-        <v>689.22</v>
-      </c>
-      <c r="AA9" s="13">
-        <v>0.65639999999999998</v>
-      </c>
-      <c r="AB9" s="6">
+        <v>4.29</v>
+      </c>
+      <c r="AA9" s="63">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="AB9" s="13">
         <f t="shared" si="2"/>
-        <v>6695.28</v>
-      </c>
-      <c r="AC9" s="14"/>
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AC9" s="65"/>
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
     </row>
@@ -3082,87 +3221,89 @@
       <c r="A10" s="52">
         <v>8</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="93" t="s">
+      <c r="B10" s="168"/>
+      <c r="C10" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="94" t="s">
+      <c r="D10" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="92" t="s">
-        <v>60</v>
+      <c r="E10" s="85" t="s">
+        <v>54</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G10" s="95" t="s">
+      <c r="G10" s="9" t="s">
         <v>81</v>
       </c>
       <c r="H10" s="66" t="s">
-        <v>256</v>
-      </c>
-      <c r="I10" s="77"/>
+        <v>250</v>
+      </c>
+      <c r="I10" s="161" t="s">
+        <v>249</v>
+      </c>
       <c r="J10" s="33" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="K10" s="36">
         <v>50</v>
       </c>
-      <c r="L10" s="128">
+      <c r="L10" s="118">
         <v>1</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10" s="11">
         <v>50</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10" s="11">
         <v>50</v>
       </c>
-      <c r="O10" s="4">
-        <v>550</v>
-      </c>
-      <c r="P10" s="4">
-        <v>1100</v>
-      </c>
-      <c r="Q10" s="4">
+      <c r="O10" s="11">
+        <v>600</v>
+      </c>
+      <c r="P10" s="11">
+        <v>1050</v>
+      </c>
+      <c r="Q10" s="11">
         <v>10500</v>
       </c>
-      <c r="R10" s="184" t="s">
+      <c r="R10" s="160" t="s">
         <v>15</v>
       </c>
       <c r="S10" s="62">
-        <v>4.8999999999999998E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="3"/>
-        <v>0.245</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="U10" s="64">
-        <v>4.8999999999999998E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="V10" s="13">
         <f t="shared" si="4"/>
-        <v>0.245</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="W10" s="63">
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="X10" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X10" s="13">
         <f t="shared" si="0"/>
-        <v>2.145</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="63">
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="Z10" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Z10" s="13">
         <f t="shared" si="1"/>
-        <v>4.29</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" s="63">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="AB10" s="6">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="AB10" s="13">
         <f t="shared" si="2"/>
-        <v>37.799999999999997</v>
+        <v>43.050000000000004</v>
       </c>
       <c r="AC10" s="65"/>
       <c r="AD10" s="8"/>
@@ -3172,91 +3313,91 @@
       <c r="A11" s="52">
         <v>9</v>
       </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="93" t="s">
+      <c r="B11" s="169"/>
+      <c r="C11" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="91" t="s">
         <v>83</v>
       </c>
       <c r="E11" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H11" s="66" t="s">
-        <v>258</v>
-      </c>
-      <c r="I11" s="185" t="s">
-        <v>257</v>
-      </c>
-      <c r="J11" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="36">
-        <v>50</v>
-      </c>
-      <c r="L11" s="128">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4">
-        <v>50</v>
-      </c>
-      <c r="N11" s="4">
-        <v>50</v>
-      </c>
-      <c r="O11" s="4">
-        <v>600</v>
-      </c>
-      <c r="P11" s="4">
-        <v>1050</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>10500</v>
-      </c>
-      <c r="R11" s="184" t="s">
+      <c r="G11" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="H11" s="131" t="s">
+        <v>253</v>
+      </c>
+      <c r="I11" s="73" t="s">
+        <v>238</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="K11" s="23">
+        <v>100</v>
+      </c>
+      <c r="L11" s="119">
+        <v>2</v>
+      </c>
+      <c r="M11" s="23">
+        <v>100</v>
+      </c>
+      <c r="N11" s="23">
+        <v>100</v>
+      </c>
+      <c r="O11" s="23">
+        <v>1200</v>
+      </c>
+      <c r="P11" s="23">
+        <v>2200</v>
+      </c>
+      <c r="Q11" s="23">
+        <v>21000</v>
+      </c>
+      <c r="R11" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="S11" s="62">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="T11" s="13">
+      <c r="S11" s="61">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="T11" s="25">
         <f t="shared" si="3"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="U11" s="64">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="V11" s="13">
+        <v>0.31</v>
+      </c>
+      <c r="U11" s="61">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="V11" s="25">
         <f t="shared" si="4"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="W11" s="63">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="X11" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="W11" s="25">
+        <v>2.3E-3</v>
+      </c>
+      <c r="X11" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Y11" s="63">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="Z11" s="6">
+        <v>2.76</v>
+      </c>
+      <c r="Y11" s="25">
+        <v>2.3E-3</v>
+      </c>
+      <c r="Z11" s="25">
         <f t="shared" si="1"/>
-        <v>5.25</v>
-      </c>
-      <c r="AA11" s="63">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="AB11" s="6">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="AA11" s="25">
+        <v>2E-3</v>
+      </c>
+      <c r="AB11" s="25">
         <f t="shared" si="2"/>
-        <v>43.050000000000004</v>
-      </c>
-      <c r="AC11" s="65"/>
+        <v>42</v>
+      </c>
+      <c r="AC11" s="26"/>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
     </row>
@@ -3264,91 +3405,93 @@
       <c r="A12" s="52">
         <v>10</v>
       </c>
-      <c r="B12" s="85"/>
-      <c r="C12" s="97" t="s">
+      <c r="B12" s="167" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="114" t="s">
+        <v>273</v>
+      </c>
+      <c r="D12" s="81" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="98" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="99" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="100" t="s">
-        <v>260</v>
-      </c>
-      <c r="H12" s="143" t="s">
-        <v>261</v>
-      </c>
-      <c r="I12" s="73" t="s">
-        <v>245</v>
-      </c>
-      <c r="J12" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="K12" s="23">
-        <v>100</v>
-      </c>
-      <c r="L12" s="129">
-        <v>2</v>
+      <c r="H12" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="I12" s="75" t="s">
+        <v>238</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="K12" s="4">
+        <v>10</v>
+      </c>
+      <c r="L12" s="3">
+        <v>3</v>
       </c>
       <c r="M12" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N12" s="4">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="O12" s="4">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="P12" s="4">
-        <v>2200</v>
+        <v>3200</v>
       </c>
       <c r="Q12" s="4">
-        <v>21000</v>
-      </c>
-      <c r="R12" s="186" t="s">
+        <v>31500</v>
+      </c>
+      <c r="R12" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="S12" s="61">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="T12" s="13">
+      <c r="S12" s="56">
+        <v>6.5799999999999997E-2</v>
+      </c>
+      <c r="T12" s="6">
         <f t="shared" si="3"/>
-        <v>0.31</v>
-      </c>
-      <c r="U12" s="61">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="V12" s="13">
+        <v>2.6319999999999997</v>
+      </c>
+      <c r="U12" s="56">
+        <v>6.5799999999999997E-2</v>
+      </c>
+      <c r="V12" s="6">
         <f t="shared" si="4"/>
-        <v>0.31</v>
-      </c>
-      <c r="W12" s="25">
-        <v>2.3E-3</v>
+        <v>4.6059999999999999</v>
+      </c>
+      <c r="W12" s="6">
+        <v>4.0099999999999997E-2</v>
       </c>
       <c r="X12" s="6">
         <f t="shared" si="0"/>
-        <v>2.76</v>
-      </c>
-      <c r="Y12" s="25">
-        <v>2.3E-3</v>
+        <v>64.16</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>4.0099999999999997E-2</v>
       </c>
       <c r="Z12" s="6">
         <f t="shared" si="1"/>
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="AA12" s="25">
-        <v>2E-3</v>
+        <v>128.32</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>3.8300000000000001E-2</v>
       </c>
       <c r="AB12" s="6">
         <f t="shared" si="2"/>
-        <v>42</v>
-      </c>
-      <c r="AC12" s="26"/>
+        <v>1206.45</v>
+      </c>
+      <c r="AC12" s="29"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
     </row>
@@ -3356,93 +3499,92 @@
       <c r="A13" s="52">
         <v>11</v>
       </c>
-      <c r="B13" s="84" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="101" t="s">
+      <c r="B13" s="168"/>
+      <c r="C13" s="95" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="87" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="85" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="F13" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="89" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="76" t="s">
-        <v>263</v>
-      </c>
-      <c r="I13" s="75" t="s">
-        <v>245</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K13" s="4">
+      <c r="H13" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="I13" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K13" s="11">
         <v>10</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="10">
         <v>3</v>
       </c>
-      <c r="M13" s="4">
-        <v>40</v>
-      </c>
-      <c r="N13" s="4">
+      <c r="M13" s="11">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="N13" s="11">
         <v>70</v>
       </c>
-      <c r="O13" s="4">
+      <c r="O13" s="11">
         <v>1600</v>
       </c>
-      <c r="P13" s="4">
-        <v>3200</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>31500</v>
-      </c>
-      <c r="R13" s="187" t="s">
-        <v>15</v>
-      </c>
-      <c r="S13" s="56">
-        <v>6.5799999999999997E-2</v>
+      <c r="P13" s="11">
+        <v>3100</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>30500</v>
+      </c>
+      <c r="R13" s="159" t="s">
+        <v>317</v>
+      </c>
+      <c r="S13" s="57">
+        <v>3.6850000000000001E-2</v>
       </c>
       <c r="T13" s="13">
         <f t="shared" si="3"/>
-        <v>2.6319999999999997</v>
-      </c>
-      <c r="U13" s="56">
-        <v>6.5799999999999997E-2</v>
+        <v>1.28975</v>
+      </c>
+      <c r="U13" s="57">
+        <v>3.6850000000000001E-2</v>
       </c>
       <c r="V13" s="13">
         <f t="shared" si="4"/>
-        <v>4.6059999999999999</v>
-      </c>
-      <c r="W13" s="6">
-        <v>4.0099999999999997E-2</v>
-      </c>
-      <c r="X13" s="6">
+        <v>2.5794999999999999</v>
+      </c>
+      <c r="W13" s="13">
+        <v>2.3619999999999999E-2</v>
+      </c>
+      <c r="X13" s="13">
         <f t="shared" si="0"/>
-        <v>64.16</v>
-      </c>
-      <c r="Y13" s="6">
-        <v>4.0099999999999997E-2</v>
-      </c>
-      <c r="Z13" s="6">
+        <v>37.791999999999994</v>
+      </c>
+      <c r="Y13" s="13">
+        <v>2.3619999999999999E-2</v>
+      </c>
+      <c r="Z13" s="13">
         <f t="shared" si="1"/>
-        <v>128.32</v>
-      </c>
-      <c r="AA13" s="6">
-        <v>3.8300000000000001E-2</v>
-      </c>
-      <c r="AB13" s="6">
+        <v>73.221999999999994</v>
+      </c>
+      <c r="AA13" s="13">
+        <v>2.2440000000000002E-2</v>
+      </c>
+      <c r="AB13" s="13">
         <f t="shared" si="2"/>
-        <v>1206.45</v>
-      </c>
-      <c r="AC13" s="29"/>
+        <v>684.42000000000007</v>
+      </c>
+      <c r="AC13" s="14"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
     </row>
@@ -3450,76 +3592,76 @@
       <c r="A14" s="52">
         <v>12</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="102" t="s">
+      <c r="B14" s="169"/>
+      <c r="C14" s="96" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="94" t="s">
+      <c r="D14" s="91" t="s">
         <v>93</v>
       </c>
       <c r="E14" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="H14" s="66"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="10">
-        <v>3</v>
-      </c>
-      <c r="M14" s="4">
+      <c r="H14" s="72"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="21">
+        <v>4</v>
+      </c>
+      <c r="M14" s="23">
         <f t="shared" si="5"/>
-        <v>35</v>
-      </c>
-      <c r="N14" s="4">
+        <v>46</v>
+      </c>
+      <c r="N14" s="23">
         <f t="shared" si="6"/>
-        <v>69</v>
-      </c>
-      <c r="O14" s="4">
-        <f t="shared" ref="O6:O40" si="7">ROUND(L14*500*1.15,0)</f>
-        <v>1725</v>
-      </c>
-      <c r="P14" s="4">
-        <f t="shared" ref="P4:P40" si="8">ROUND(L14*1000*1.15,0)</f>
-        <v>3450</v>
-      </c>
-      <c r="Q14" s="4">
-        <f t="shared" ref="Q4:Q40" si="9">ROUND(L14*10000*1.15,0)</f>
-        <v>34500</v>
-      </c>
-      <c r="R14" s="17"/>
-      <c r="S14" s="57"/>
-      <c r="T14" s="13">
+        <v>92</v>
+      </c>
+      <c r="O14" s="23">
+        <f t="shared" ref="O13:O38" si="7">ROUND(L14*500*1.15,0)</f>
+        <v>2300</v>
+      </c>
+      <c r="P14" s="23">
+        <f t="shared" ref="P13:P38" si="8">ROUND(L14*1000*1.15,0)</f>
+        <v>4600</v>
+      </c>
+      <c r="Q14" s="23">
+        <f t="shared" ref="Q13:Q38" si="9">ROUND(L14*10000*1.15,0)</f>
+        <v>46000</v>
+      </c>
+      <c r="R14" s="24"/>
+      <c r="S14" s="61"/>
+      <c r="T14" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U14" s="57"/>
-      <c r="V14" s="13">
+      <c r="U14" s="61"/>
+      <c r="V14" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W14" s="13"/>
-      <c r="X14" s="6">
+      <c r="W14" s="25"/>
+      <c r="X14" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="6">
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="6">
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="14"/>
+      <c r="AC14" s="26"/>
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
     </row>
@@ -3527,76 +3669,93 @@
       <c r="A15" s="52">
         <v>13</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="103" t="s">
+      <c r="B15" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="98" t="s">
+      <c r="C15" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="99" t="s">
+      <c r="D15" s="99" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="E15" s="136" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="101" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="72"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="21">
-        <v>4</v>
-      </c>
-      <c r="M15" s="4">
-        <f t="shared" si="5"/>
-        <v>46</v>
-      </c>
-      <c r="N15" s="4">
-        <f t="shared" si="6"/>
-        <v>92</v>
-      </c>
-      <c r="O15" s="4">
-        <f t="shared" si="7"/>
-        <v>2300</v>
-      </c>
-      <c r="P15" s="4">
-        <f t="shared" si="8"/>
-        <v>4600</v>
-      </c>
-      <c r="Q15" s="4">
-        <f t="shared" si="9"/>
-        <v>46000</v>
-      </c>
-      <c r="R15" s="24"/>
-      <c r="S15" s="61"/>
-      <c r="T15" s="13">
+      <c r="G15" s="102" t="s">
+        <v>256</v>
+      </c>
+      <c r="H15" s="137" t="s">
+        <v>257</v>
+      </c>
+      <c r="I15" s="138" t="s">
+        <v>238</v>
+      </c>
+      <c r="J15" s="139" t="s">
+        <v>238</v>
+      </c>
+      <c r="K15" s="140">
+        <v>10</v>
+      </c>
+      <c r="L15" s="121">
+        <v>2</v>
+      </c>
+      <c r="M15" s="140">
+        <v>20</v>
+      </c>
+      <c r="N15" s="140">
+        <v>50</v>
+      </c>
+      <c r="O15" s="140">
+        <v>1050</v>
+      </c>
+      <c r="P15" s="140">
+        <v>2100</v>
+      </c>
+      <c r="Q15" s="140">
+        <v>21000</v>
+      </c>
+      <c r="R15" s="164" t="s">
+        <v>15</v>
+      </c>
+      <c r="S15" s="141">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="T15" s="142">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="61"/>
-      <c r="V15" s="13">
+        <v>0.90999999999999992</v>
+      </c>
+      <c r="U15" s="141">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="V15" s="142">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="25"/>
-      <c r="X15" s="6">
+        <v>2.2749999999999999</v>
+      </c>
+      <c r="W15" s="142">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="X15" s="142">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="6">
+        <v>32.129999999999995</v>
+      </c>
+      <c r="Y15" s="142">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="Z15" s="142">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="6">
+        <v>64.259999999999991</v>
+      </c>
+      <c r="AA15" s="142">
+        <v>2.93E-2</v>
+      </c>
+      <c r="AB15" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="26"/>
+        <v>615.29999999999995</v>
+      </c>
+      <c r="AC15" s="178"/>
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
     </row>
@@ -3604,93 +3763,93 @@
       <c r="A16" s="52">
         <v>14</v>
       </c>
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="167" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="81" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="108" t="s">
+      <c r="F16" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="109" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" s="149" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="111" t="s">
-        <v>105</v>
-      </c>
-      <c r="G16" s="112" t="s">
-        <v>264</v>
-      </c>
-      <c r="H16" s="150" t="s">
-        <v>265</v>
-      </c>
-      <c r="I16" s="151" t="s">
-        <v>245</v>
-      </c>
-      <c r="J16" s="152" t="s">
-        <v>245</v>
-      </c>
-      <c r="K16" s="153">
+      <c r="G16" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J16" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="K16" s="132">
+        <v>5</v>
+      </c>
+      <c r="L16" s="117">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4">
         <v>10</v>
       </c>
-      <c r="L16" s="132">
-        <v>2</v>
-      </c>
-      <c r="M16" s="4">
-        <v>20</v>
-      </c>
       <c r="N16" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O16" s="4">
+        <v>525</v>
+      </c>
+      <c r="P16" s="4">
         <v>1050</v>
       </c>
-      <c r="P16" s="4">
-        <v>2100</v>
-      </c>
       <c r="Q16" s="4">
-        <v>21000</v>
-      </c>
-      <c r="R16" s="188" t="s">
+        <v>10500</v>
+      </c>
+      <c r="R16" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="S16" s="154">
-        <v>4.5499999999999999E-2</v>
-      </c>
-      <c r="T16" s="13">
+      <c r="S16" s="133">
+        <v>8.0799999999999997E-2</v>
+      </c>
+      <c r="T16" s="6">
         <f t="shared" si="3"/>
-        <v>0.90999999999999992</v>
-      </c>
-      <c r="U16" s="154">
-        <v>4.5499999999999999E-2</v>
-      </c>
-      <c r="V16" s="13">
+        <v>0.80799999999999994</v>
+      </c>
+      <c r="U16" s="133">
+        <v>8.0799999999999997E-2</v>
+      </c>
+      <c r="V16" s="6">
         <f t="shared" si="4"/>
-        <v>2.2749999999999999</v>
-      </c>
-      <c r="W16" s="155">
-        <v>3.0599999999999999E-2</v>
+        <v>2.02</v>
+      </c>
+      <c r="W16" s="134">
+        <v>5.4300000000000001E-2</v>
       </c>
       <c r="X16" s="6">
         <f t="shared" si="0"/>
-        <v>32.129999999999995</v>
-      </c>
-      <c r="Y16" s="155">
-        <v>3.0599999999999999E-2</v>
+        <v>28.5075</v>
+      </c>
+      <c r="Y16" s="134">
+        <v>5.4300000000000001E-2</v>
       </c>
       <c r="Z16" s="6">
         <f t="shared" si="1"/>
-        <v>64.259999999999991</v>
-      </c>
-      <c r="AA16" s="155">
-        <v>2.93E-2</v>
+        <v>57.015000000000001</v>
+      </c>
+      <c r="AA16" s="134">
+        <v>5.1900000000000002E-2</v>
       </c>
       <c r="AB16" s="6">
         <f t="shared" si="2"/>
-        <v>615.29999999999995</v>
-      </c>
-      <c r="AC16" s="156"/>
+        <v>544.95000000000005</v>
+      </c>
+      <c r="AC16" s="135"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
     </row>
@@ -3698,93 +3857,92 @@
       <c r="A17" s="52">
         <v>15</v>
       </c>
-      <c r="B17" s="84" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="101" t="s">
+      <c r="B17" s="168"/>
+      <c r="C17" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="88" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="89" t="s">
-        <v>107</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J17" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="K17" s="144">
-        <v>5</v>
-      </c>
-      <c r="L17" s="127">
+      <c r="G17" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="H17" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>238</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K17" s="11">
         <v>1</v>
       </c>
-      <c r="M17" s="4">
-        <v>10</v>
-      </c>
-      <c r="N17" s="4">
-        <v>25</v>
-      </c>
-      <c r="O17" s="4">
-        <v>525</v>
-      </c>
-      <c r="P17" s="4">
+      <c r="L17" s="118">
+        <v>1</v>
+      </c>
+      <c r="M17" s="11">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="N17" s="11">
+        <v>22</v>
+      </c>
+      <c r="O17" s="11">
+        <v>520</v>
+      </c>
+      <c r="P17" s="11">
         <v>1050</v>
       </c>
-      <c r="Q17" s="4">
-        <v>10500</v>
-      </c>
-      <c r="R17" s="187" t="s">
+      <c r="Q17" s="11">
+        <v>10200</v>
+      </c>
+      <c r="R17" s="159" t="s">
         <v>15</v>
       </c>
-      <c r="S17" s="146">
-        <v>8.0799999999999997E-2</v>
+      <c r="S17" s="57">
+        <v>0.1492</v>
       </c>
       <c r="T17" s="13">
         <f t="shared" si="3"/>
-        <v>0.80799999999999994</v>
-      </c>
-      <c r="U17" s="146">
-        <v>8.0799999999999997E-2</v>
+        <v>1.7904</v>
+      </c>
+      <c r="U17" s="57">
+        <v>0.1492</v>
       </c>
       <c r="V17" s="13">
         <f t="shared" si="4"/>
-        <v>2.02</v>
-      </c>
-      <c r="W17" s="147">
-        <v>5.4300000000000001E-2</v>
-      </c>
-      <c r="X17" s="6">
+        <v>3.2824</v>
+      </c>
+      <c r="W17" s="13">
+        <v>0.128</v>
+      </c>
+      <c r="X17" s="13">
         <f t="shared" si="0"/>
-        <v>28.5075</v>
-      </c>
-      <c r="Y17" s="147">
-        <v>5.4300000000000001E-2</v>
-      </c>
-      <c r="Z17" s="6">
+        <v>66.56</v>
+      </c>
+      <c r="Y17" s="13">
+        <v>0.12609999999999999</v>
+      </c>
+      <c r="Z17" s="13">
         <f t="shared" si="1"/>
-        <v>57.015000000000001</v>
-      </c>
-      <c r="AA17" s="147">
-        <v>5.1900000000000002E-2</v>
-      </c>
-      <c r="AB17" s="6">
+        <v>132.405</v>
+      </c>
+      <c r="AA17" s="13">
+        <v>0.12609999999999999</v>
+      </c>
+      <c r="AB17" s="13">
         <f t="shared" si="2"/>
-        <v>544.95000000000005</v>
-      </c>
-      <c r="AC17" s="148"/>
+        <v>1286.2199999999998</v>
+      </c>
+      <c r="AC17" s="38"/>
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
     </row>
@@ -3792,92 +3950,91 @@
       <c r="A18" s="52">
         <v>16</v>
       </c>
-      <c r="B18" s="83"/>
-      <c r="C18" s="107" t="s">
+      <c r="B18" s="169"/>
+      <c r="C18" s="96" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="91" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="94" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="H18" s="78" t="s">
-        <v>268</v>
-      </c>
-      <c r="I18" s="68" t="s">
-        <v>245</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="K18" s="11">
+      <c r="G18" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="H18" s="71" t="s">
+        <v>262</v>
+      </c>
+      <c r="I18" s="72" t="s">
+        <v>238</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="K18" s="23">
+        <v>10</v>
+      </c>
+      <c r="L18" s="119">
         <v>1</v>
       </c>
-      <c r="L18" s="128">
-        <v>1</v>
-      </c>
-      <c r="M18" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N18" s="4">
-        <v>22</v>
-      </c>
-      <c r="O18" s="4">
-        <v>520</v>
-      </c>
-      <c r="P18" s="4">
+      <c r="M18" s="23">
+        <v>10</v>
+      </c>
+      <c r="N18" s="23">
+        <v>20</v>
+      </c>
+      <c r="O18" s="23">
+        <v>550</v>
+      </c>
+      <c r="P18" s="23">
         <v>1050</v>
       </c>
-      <c r="Q18" s="4">
-        <v>10200</v>
-      </c>
-      <c r="R18" s="183" t="s">
+      <c r="Q18" s="23">
+        <v>10500</v>
+      </c>
+      <c r="R18" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="S18" s="57">
-        <v>0.1492</v>
-      </c>
-      <c r="T18" s="13">
+      <c r="S18" s="61">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="T18" s="25">
         <f t="shared" si="3"/>
-        <v>1.7904</v>
-      </c>
-      <c r="U18" s="57">
-        <v>0.1492</v>
-      </c>
-      <c r="V18" s="13">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="U18" s="61">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="V18" s="25">
         <f t="shared" si="4"/>
-        <v>3.2824</v>
-      </c>
-      <c r="W18" s="13">
-        <v>0.128</v>
-      </c>
-      <c r="X18" s="6">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="W18" s="25">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="X18" s="25">
         <f t="shared" si="0"/>
-        <v>66.56</v>
-      </c>
-      <c r="Y18" s="13">
-        <v>0.12609999999999999</v>
-      </c>
-      <c r="Z18" s="6">
+        <v>20.68</v>
+      </c>
+      <c r="Y18" s="25">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="Z18" s="25">
         <f t="shared" si="1"/>
-        <v>132.405</v>
-      </c>
-      <c r="AA18" s="13">
-        <v>0.12609999999999999</v>
-      </c>
-      <c r="AB18" s="6">
+        <v>37.484999999999999</v>
+      </c>
+      <c r="AA18" s="25">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="AB18" s="25">
         <f t="shared" si="2"/>
-        <v>1286.2199999999998</v>
-      </c>
-      <c r="AC18" s="38"/>
+        <v>362.25000000000006</v>
+      </c>
+      <c r="AC18" s="26"/>
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
     </row>
@@ -3885,91 +4042,78 @@
       <c r="A19" s="52">
         <v>17</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="103" t="s">
+      <c r="B19" s="167" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="94" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="81" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="E19" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="99" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G19" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="H19" s="71" t="s">
-        <v>270</v>
-      </c>
-      <c r="I19" s="72" t="s">
-        <v>245</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="K19" s="23">
-        <v>10</v>
-      </c>
-      <c r="L19" s="129">
+      <c r="G19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" s="76"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="117">
         <v>1</v>
       </c>
       <c r="M19" s="4">
-        <v>10</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="N19" s="4">
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="O19" s="4">
-        <v>550</v>
+        <f t="shared" si="7"/>
+        <v>575</v>
       </c>
       <c r="P19" s="4">
-        <v>1050</v>
+        <f t="shared" si="8"/>
+        <v>1150</v>
       </c>
       <c r="Q19" s="4">
-        <v>10500</v>
-      </c>
-      <c r="R19" s="186" t="s">
-        <v>15</v>
-      </c>
-      <c r="S19" s="61">
-        <v>4.9299999999999997E-2</v>
-      </c>
-      <c r="T19" s="13">
+        <f t="shared" si="9"/>
+        <v>11500</v>
+      </c>
+      <c r="R19" s="5"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="6">
         <f t="shared" si="3"/>
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="U19" s="61">
-        <v>4.9299999999999997E-2</v>
-      </c>
-      <c r="V19" s="13">
+        <v>0</v>
+      </c>
+      <c r="U19" s="56"/>
+      <c r="V19" s="6">
         <f t="shared" si="4"/>
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="W19" s="25">
-        <v>3.7600000000000001E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W19" s="6"/>
       <c r="X19" s="6">
         <f t="shared" si="0"/>
-        <v>20.68</v>
-      </c>
-      <c r="Y19" s="25">
-        <v>3.5700000000000003E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="6"/>
       <c r="Z19" s="6">
         <f t="shared" si="1"/>
-        <v>37.484999999999999</v>
-      </c>
-      <c r="AA19" s="25">
-        <v>3.4500000000000003E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="6"/>
       <c r="AB19" s="6">
         <f t="shared" si="2"/>
-        <v>362.25000000000006</v>
-      </c>
-      <c r="AC19" s="26"/>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="7"/>
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
     </row>
@@ -3977,78 +4121,76 @@
       <c r="A20" s="52">
         <v>18</v>
       </c>
-      <c r="B20" s="84" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="101" t="s">
+      <c r="B20" s="169"/>
+      <c r="C20" s="96" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="88" t="s">
+      <c r="D20" s="91" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="89" t="s">
+      <c r="E20" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H20" s="76"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="127">
-        <v>1</v>
-      </c>
-      <c r="M20" s="4">
+      <c r="H20" s="131"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="119">
+        <v>3</v>
+      </c>
+      <c r="M20" s="23">
         <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N20" s="4">
+        <v>35</v>
+      </c>
+      <c r="N20" s="23">
         <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O20" s="4">
+        <v>69</v>
+      </c>
+      <c r="O20" s="23">
         <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P20" s="4">
+        <v>1725</v>
+      </c>
+      <c r="P20" s="23">
         <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q20" s="4">
+        <v>3450</v>
+      </c>
+      <c r="Q20" s="23">
         <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R20" s="5"/>
-      <c r="S20" s="56"/>
-      <c r="T20" s="13">
+        <v>34500</v>
+      </c>
+      <c r="R20" s="143"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U20" s="56"/>
-      <c r="V20" s="13">
+      <c r="U20" s="61"/>
+      <c r="V20" s="25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6">
+      <c r="W20" s="25"/>
+      <c r="X20" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6">
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="6"/>
-      <c r="AB20" s="6">
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC20" s="7"/>
+      <c r="AC20" s="26"/>
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
     </row>
@@ -4056,76 +4198,93 @@
       <c r="A21" s="52">
         <v>19</v>
       </c>
-      <c r="B21" s="85"/>
-      <c r="C21" s="103" t="s">
+      <c r="B21" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="100" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="101" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="98" t="s">
+      <c r="G21" s="102" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="99" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21" s="143"/>
-      <c r="I21" s="143"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="129">
+      <c r="H21" s="144" t="s">
+        <v>263</v>
+      </c>
+      <c r="I21" s="137" t="s">
+        <v>238</v>
+      </c>
+      <c r="J21" s="145" t="s">
+        <v>238</v>
+      </c>
+      <c r="K21" s="146">
+        <v>10</v>
+      </c>
+      <c r="L21" s="120">
         <v>3</v>
       </c>
-      <c r="M21" s="4">
-        <f t="shared" si="5"/>
-        <v>35</v>
-      </c>
-      <c r="N21" s="4">
-        <f t="shared" si="6"/>
-        <v>69</v>
-      </c>
-      <c r="O21" s="4">
-        <f t="shared" si="7"/>
-        <v>1725</v>
-      </c>
-      <c r="P21" s="4">
-        <f t="shared" si="8"/>
-        <v>3450</v>
-      </c>
-      <c r="Q21" s="4">
-        <f t="shared" si="9"/>
-        <v>34500</v>
-      </c>
-      <c r="R21" s="157"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="13">
+      <c r="M21" s="140">
+        <v>30</v>
+      </c>
+      <c r="N21" s="140">
+        <v>70</v>
+      </c>
+      <c r="O21" s="140">
+        <v>1600</v>
+      </c>
+      <c r="P21" s="140">
+        <v>3150</v>
+      </c>
+      <c r="Q21" s="140">
+        <v>31500</v>
+      </c>
+      <c r="R21" s="165" t="s">
+        <v>15</v>
+      </c>
+      <c r="S21" s="147">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="T21" s="142">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="61"/>
-      <c r="V21" s="13">
+        <v>1.611</v>
+      </c>
+      <c r="U21" s="147">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="V21" s="142">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="25"/>
-      <c r="X21" s="6">
+        <v>3.7589999999999999</v>
+      </c>
+      <c r="W21" s="148">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="X21" s="142">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="6">
+        <v>57.28</v>
+      </c>
+      <c r="Y21" s="148">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="Z21" s="142">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="25"/>
-      <c r="AB21" s="6">
+        <v>112.77</v>
+      </c>
+      <c r="AA21" s="148">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="AB21" s="142">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC21" s="26"/>
+        <v>1077.3</v>
+      </c>
+      <c r="AC21" s="179"/>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
     </row>
@@ -4133,93 +4292,94 @@
       <c r="A22" s="52">
         <v>20</v>
       </c>
-      <c r="B22" s="79" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="108" t="s">
+      <c r="B22" s="167" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="109" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="110" t="s">
+      <c r="E22" s="82" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="111" t="s">
+      <c r="F22" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="G22" s="112" t="s">
-        <v>127</v>
-      </c>
-      <c r="H22" s="158" t="s">
-        <v>271</v>
-      </c>
-      <c r="I22" s="150" t="s">
-        <v>245</v>
-      </c>
-      <c r="J22" s="159" t="s">
-        <v>245</v>
-      </c>
-      <c r="K22" s="160">
-        <v>10</v>
-      </c>
-      <c r="L22" s="131">
-        <v>3</v>
+      <c r="G22" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H22" s="76" t="s">
+        <v>265</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="K22" s="4">
+        <v>5</v>
+      </c>
+      <c r="L22" s="117">
+        <v>1</v>
       </c>
       <c r="M22" s="4">
-        <v>30</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="N22" s="4">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="O22" s="4">
-        <v>1600</v>
+        <v>525</v>
       </c>
       <c r="P22" s="4">
-        <v>3150</v>
+        <v>1050</v>
       </c>
       <c r="Q22" s="4">
-        <v>31500</v>
-      </c>
-      <c r="R22" s="189" t="s">
+        <v>10500</v>
+      </c>
+      <c r="R22" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="S22" s="161">
-        <v>5.3699999999999998E-2</v>
-      </c>
-      <c r="T22" s="13">
+      <c r="S22" s="56">
+        <v>0.1138</v>
+      </c>
+      <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>1.611</v>
-      </c>
-      <c r="U22" s="161">
-        <v>5.3699999999999998E-2</v>
-      </c>
-      <c r="V22" s="13">
+        <v>1.3655999999999999</v>
+      </c>
+      <c r="U22" s="56">
+        <v>0.1138</v>
+      </c>
+      <c r="V22" s="6">
         <f t="shared" si="4"/>
-        <v>3.7589999999999999</v>
-      </c>
-      <c r="W22" s="162">
-        <v>3.5799999999999998E-2</v>
+        <v>2.8449999999999998</v>
+      </c>
+      <c r="W22" s="6">
+        <v>7.0400000000000004E-2</v>
       </c>
       <c r="X22" s="6">
         <f t="shared" si="0"/>
-        <v>57.28</v>
-      </c>
-      <c r="Y22" s="162">
-        <v>3.5799999999999998E-2</v>
+        <v>36.96</v>
+      </c>
+      <c r="Y22" s="6">
+        <v>7.0400000000000004E-2</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="1"/>
-        <v>112.77</v>
-      </c>
-      <c r="AA22" s="162">
-        <v>3.4200000000000001E-2</v>
+        <v>73.92</v>
+      </c>
+      <c r="AA22" s="6">
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="2"/>
-        <v>1077.3</v>
-      </c>
-      <c r="AC22" s="160"/>
+        <v>708.75</v>
+      </c>
+      <c r="AC22" s="7"/>
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
     </row>
@@ -4227,94 +4387,91 @@
       <c r="A23" s="52">
         <v>21</v>
       </c>
-      <c r="B23" s="84" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="101" t="s">
+      <c r="B23" s="168"/>
+      <c r="C23" s="97" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="88" t="s">
-        <v>129</v>
-      </c>
-      <c r="E23" s="89" t="s">
-        <v>130</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H23" s="76" t="s">
-        <v>273</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="K23" s="4">
-        <v>5</v>
-      </c>
-      <c r="L23" s="127">
-        <v>1</v>
-      </c>
-      <c r="M23" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N23" s="4">
-        <v>25</v>
-      </c>
-      <c r="O23" s="4">
-        <v>525</v>
-      </c>
-      <c r="P23" s="4">
-        <v>1050</v>
-      </c>
-      <c r="Q23" s="4">
-        <v>10500</v>
-      </c>
-      <c r="R23" s="187" t="s">
+      <c r="E23" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H23" s="66" t="s">
+        <v>266</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="J23" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="9">
+        <v>100</v>
+      </c>
+      <c r="L23" s="118">
+        <v>3</v>
+      </c>
+      <c r="M23" s="11">
+        <v>100</v>
+      </c>
+      <c r="N23" s="11">
+        <v>100</v>
+      </c>
+      <c r="O23" s="11">
+        <v>1600</v>
+      </c>
+      <c r="P23" s="11">
+        <v>3200</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>32000</v>
+      </c>
+      <c r="R23" s="159" t="s">
         <v>15</v>
       </c>
-      <c r="S23" s="56">
-        <v>0.1138</v>
+      <c r="S23" s="57">
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="T23" s="13">
         <f t="shared" si="3"/>
-        <v>1.3655999999999999</v>
-      </c>
-      <c r="U23" s="56">
-        <v>0.1138</v>
+        <v>0.13</v>
+      </c>
+      <c r="U23" s="57">
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="V23" s="13">
         <f t="shared" si="4"/>
-        <v>2.8449999999999998</v>
-      </c>
-      <c r="W23" s="6">
-        <v>7.0400000000000004E-2</v>
-      </c>
-      <c r="X23" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="W23" s="13">
+        <v>1E-3</v>
+      </c>
+      <c r="X23" s="13">
         <f t="shared" si="0"/>
-        <v>36.96</v>
-      </c>
-      <c r="Y23" s="6">
-        <v>7.0400000000000004E-2</v>
-      </c>
-      <c r="Z23" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="Y23" s="13">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Z23" s="13">
         <f t="shared" si="1"/>
-        <v>73.92</v>
-      </c>
-      <c r="AA23" s="6">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="AB23" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="AA23" s="13">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="AB23" s="13">
         <f t="shared" si="2"/>
-        <v>708.75</v>
-      </c>
-      <c r="AC23" s="7"/>
+        <v>25.6</v>
+      </c>
+      <c r="AC23" s="14"/>
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
     </row>
@@ -4322,85 +4479,93 @@
       <c r="A24" s="52">
         <v>22</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="107" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="66"/>
+      <c r="B24" s="168"/>
+      <c r="C24" s="199" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="87" t="s">
+        <v>271</v>
+      </c>
+      <c r="E24" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H24" s="66" t="s">
+        <v>266</v>
+      </c>
       <c r="I24" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="J24" s="190" t="s">
-        <v>35</v>
-      </c>
-      <c r="K24" s="9">
+        <v>238</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="K24" s="15">
         <v>100</v>
       </c>
-      <c r="L24" s="128">
-        <v>3</v>
-      </c>
-      <c r="M24" s="4">
+      <c r="L24" s="118">
+        <v>5</v>
+      </c>
+      <c r="M24" s="11">
         <v>100</v>
       </c>
-      <c r="N24" s="4">
-        <v>100</v>
-      </c>
-      <c r="O24" s="4">
-        <v>1600</v>
-      </c>
-      <c r="P24" s="4">
-        <v>3200</v>
-      </c>
-      <c r="Q24" s="4">
-        <v>32000</v>
-      </c>
-      <c r="R24" s="183" t="s">
+      <c r="N24" s="11">
+        <v>200</v>
+      </c>
+      <c r="O24" s="11">
+        <v>2600</v>
+      </c>
+      <c r="P24" s="11">
+        <v>5200</v>
+      </c>
+      <c r="Q24" s="11">
+        <v>52000</v>
+      </c>
+      <c r="R24" s="129" t="s">
         <v>15</v>
       </c>
-      <c r="S24" s="57">
+      <c r="S24" s="59">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="T24" s="13">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
-      <c r="U24" s="57">
+      <c r="U24" s="59">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="V24" s="13">
         <f t="shared" si="4"/>
-        <v>0.13</v>
-      </c>
-      <c r="W24" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="W24" s="60">
         <v>1E-3</v>
       </c>
-      <c r="X24" s="6">
+      <c r="X24" s="13">
         <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-      <c r="Y24" s="13">
+        <v>2.6</v>
+      </c>
+      <c r="Y24" s="60">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Z24" s="6">
+      <c r="Z24" s="13">
         <f t="shared" si="1"/>
-        <v>2.88</v>
-      </c>
-      <c r="AA24" s="13">
+        <v>4.68</v>
+      </c>
+      <c r="AA24" s="60">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="AB24" s="6">
+      <c r="AB24" s="13">
         <f t="shared" si="2"/>
-        <v>25.6</v>
-      </c>
-      <c r="AC24" s="14"/>
+        <v>41.6</v>
+      </c>
+      <c r="AC24" s="39" t="s">
+        <v>314</v>
+      </c>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
     </row>
@@ -4408,91 +4573,91 @@
       <c r="A25" s="52">
         <v>23</v>
       </c>
-      <c r="B25" s="83"/>
-      <c r="C25" s="191" t="s">
-        <v>135</v>
-      </c>
-      <c r="D25" s="94" t="s">
-        <v>280</v>
-      </c>
-      <c r="E25" s="92" t="s">
-        <v>55</v>
+      <c r="B25" s="168"/>
+      <c r="C25" s="97" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="85" t="s">
+        <v>54</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>247</v>
+        <v>56</v>
       </c>
       <c r="H25" s="66" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="K25" s="15">
+        <v>269</v>
+      </c>
+      <c r="K25" s="9">
         <v>100</v>
       </c>
-      <c r="L25" s="128">
-        <v>5</v>
-      </c>
-      <c r="M25" s="4">
+      <c r="L25" s="118">
+        <v>1</v>
+      </c>
+      <c r="M25" s="11">
         <v>100</v>
       </c>
-      <c r="N25" s="4">
-        <v>200</v>
-      </c>
-      <c r="O25" s="4">
-        <v>2600</v>
-      </c>
-      <c r="P25" s="4">
-        <v>5200</v>
-      </c>
-      <c r="Q25" s="4">
-        <v>52000</v>
-      </c>
-      <c r="R25" s="141" t="s">
+      <c r="N25" s="11">
+        <v>100</v>
+      </c>
+      <c r="O25" s="11">
+        <v>600</v>
+      </c>
+      <c r="P25" s="11">
+        <v>1100</v>
+      </c>
+      <c r="Q25" s="11">
+        <v>10500</v>
+      </c>
+      <c r="R25" s="159" t="s">
         <v>15</v>
       </c>
-      <c r="S25" s="59">
-        <v>1.2999999999999999E-3</v>
+      <c r="S25" s="57">
+        <v>1.9E-3</v>
       </c>
       <c r="T25" s="13">
         <f t="shared" si="3"/>
-        <v>0.13</v>
-      </c>
-      <c r="U25" s="59">
-        <v>1.2999999999999999E-3</v>
+        <v>0.19</v>
+      </c>
+      <c r="U25" s="57">
+        <v>1.9E-3</v>
       </c>
       <c r="V25" s="13">
         <f t="shared" si="4"/>
-        <v>0.26</v>
-      </c>
-      <c r="W25" s="60">
-        <v>1E-3</v>
-      </c>
-      <c r="X25" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="W25" s="13">
+        <v>1.9E-3</v>
+      </c>
+      <c r="X25" s="13">
         <f t="shared" si="0"/>
-        <v>2.6</v>
-      </c>
-      <c r="Y25" s="60">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="Z25" s="6">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="Y25" s="13">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Z25" s="13">
         <f t="shared" si="1"/>
-        <v>4.68</v>
-      </c>
-      <c r="AA25" s="60">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="AB25" s="6">
+        <v>1.76</v>
+      </c>
+      <c r="AA25" s="13">
+        <v>1.4E-3</v>
+      </c>
+      <c r="AB25" s="13">
         <f t="shared" si="2"/>
-        <v>41.6</v>
-      </c>
-      <c r="AC25" s="39"/>
+        <v>14.7</v>
+      </c>
+      <c r="AC25" s="14"/>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
     </row>
@@ -4500,89 +4665,89 @@
       <c r="A26" s="52">
         <v>24</v>
       </c>
-      <c r="B26" s="83"/>
-      <c r="C26" s="107" t="s">
+      <c r="B26" s="168"/>
+      <c r="C26" s="95" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" s="87" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D26" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>57</v>
-      </c>
       <c r="H26" s="66" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K26" s="9">
-        <v>100</v>
-      </c>
-      <c r="L26" s="128">
+        <v>50</v>
+      </c>
+      <c r="L26" s="118">
         <v>1</v>
       </c>
-      <c r="M26" s="4">
-        <v>100</v>
-      </c>
-      <c r="N26" s="4">
-        <v>100</v>
-      </c>
-      <c r="O26" s="4">
-        <v>600</v>
-      </c>
-      <c r="P26" s="4">
-        <v>1100</v>
-      </c>
-      <c r="Q26" s="4">
+      <c r="M26" s="11">
+        <v>50</v>
+      </c>
+      <c r="N26" s="11">
+        <v>50</v>
+      </c>
+      <c r="O26" s="11">
+        <v>550</v>
+      </c>
+      <c r="P26" s="11">
+        <v>1050</v>
+      </c>
+      <c r="Q26" s="11">
         <v>10500</v>
       </c>
-      <c r="R26" s="183" t="s">
+      <c r="R26" s="159" t="s">
         <v>15</v>
       </c>
       <c r="S26" s="57">
-        <v>1.9E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="T26" s="13">
         <f t="shared" si="3"/>
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="U26" s="57">
-        <v>1.9E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="V26" s="13">
         <f t="shared" si="4"/>
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="W26" s="13">
-        <v>1.9E-3</v>
-      </c>
-      <c r="X26" s="6">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="X26" s="13">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>2.145</v>
       </c>
       <c r="Y26" s="13">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="Z26" s="6">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="Z26" s="13">
         <f t="shared" si="1"/>
-        <v>1.76</v>
+        <v>4.0949999999999998</v>
       </c>
       <c r="AA26" s="13">
-        <v>1.4E-3</v>
-      </c>
-      <c r="AB26" s="6">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="AB26" s="13">
         <f t="shared" si="2"/>
-        <v>14.7</v>
+        <v>35.699999999999996</v>
       </c>
       <c r="AC26" s="14"/>
       <c r="AD26" s="8"/>
@@ -4592,74 +4757,89 @@
       <c r="A27" s="52">
         <v>25</v>
       </c>
-      <c r="B27" s="83"/>
-      <c r="C27" s="102" t="s">
+      <c r="B27" s="168"/>
+      <c r="C27" s="97" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="87" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="94" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="92" t="s">
-        <v>55</v>
-      </c>
       <c r="F27" s="16" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H27" s="66"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="128">
+        <v>270</v>
+      </c>
+      <c r="H27" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="K27" s="9">
+        <v>50</v>
+      </c>
+      <c r="L27" s="118">
         <v>1</v>
       </c>
-      <c r="M27" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N27" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O27" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P27" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q27" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R27" s="17"/>
-      <c r="S27" s="57"/>
+      <c r="M27" s="11">
+        <v>50</v>
+      </c>
+      <c r="N27" s="11">
+        <v>50</v>
+      </c>
+      <c r="O27" s="11">
+        <v>550</v>
+      </c>
+      <c r="P27" s="11">
+        <v>1050</v>
+      </c>
+      <c r="Q27" s="11">
+        <v>10500</v>
+      </c>
+      <c r="R27" s="159" t="s">
+        <v>15</v>
+      </c>
+      <c r="S27" s="57">
+        <v>0.02</v>
+      </c>
       <c r="T27" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="57"/>
+        <v>1</v>
+      </c>
+      <c r="U27" s="57">
+        <v>0.02</v>
+      </c>
       <c r="V27" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="13"/>
-      <c r="X27" s="6">
+        <v>1</v>
+      </c>
+      <c r="W27" s="13">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="X27" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="6">
+        <v>8.6900000000000013</v>
+      </c>
+      <c r="Y27" s="13">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="Z27" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="6">
+        <v>16.59</v>
+      </c>
+      <c r="AA27" s="13">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AB27" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>149.10000000000002</v>
       </c>
       <c r="AC27" s="14"/>
       <c r="AD27" s="8"/>
@@ -4669,89 +4849,72 @@
       <c r="A28" s="52">
         <v>26</v>
       </c>
-      <c r="B28" s="83"/>
-      <c r="C28" s="107" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="92" t="s">
-        <v>143</v>
+      <c r="B28" s="168"/>
+      <c r="C28" s="97" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="87" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" s="85" t="s">
+        <v>54</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="H28" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="9">
-        <v>50</v>
-      </c>
-      <c r="L28" s="128">
+        <v>141</v>
+      </c>
+      <c r="G28" s="9"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="118">
         <v>1</v>
       </c>
-      <c r="M28" s="4">
-        <v>50</v>
-      </c>
-      <c r="N28" s="4">
-        <v>50</v>
-      </c>
-      <c r="O28" s="4">
-        <v>550</v>
-      </c>
-      <c r="P28" s="4">
-        <v>1050</v>
-      </c>
-      <c r="Q28" s="4">
-        <v>10500</v>
-      </c>
-      <c r="R28" s="183" t="s">
-        <v>15</v>
-      </c>
-      <c r="S28" s="57">
-        <v>0.02</v>
-      </c>
+      <c r="M28" s="11">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="N28" s="11">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="O28" s="11">
+        <f t="shared" si="7"/>
+        <v>575</v>
+      </c>
+      <c r="P28" s="11">
+        <f t="shared" si="8"/>
+        <v>1150</v>
+      </c>
+      <c r="Q28" s="11">
+        <f t="shared" si="9"/>
+        <v>11500</v>
+      </c>
+      <c r="R28" s="17"/>
+      <c r="S28" s="57"/>
       <c r="T28" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="U28" s="57">
-        <v>0.02</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U28" s="57"/>
       <c r="V28" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="W28" s="13">
-        <v>1.5800000000000002E-2</v>
-      </c>
-      <c r="X28" s="6">
+        <v>0</v>
+      </c>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13">
         <f t="shared" si="0"/>
-        <v>8.6900000000000013</v>
-      </c>
-      <c r="Y28" s="13">
-        <v>1.5800000000000002E-2</v>
-      </c>
-      <c r="Z28" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13">
         <f t="shared" si="1"/>
-        <v>16.59</v>
-      </c>
-      <c r="AA28" s="13">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="AB28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13">
         <f t="shared" si="2"/>
-        <v>149.10000000000002</v>
+        <v>0</v>
       </c>
       <c r="AC28" s="14"/>
       <c r="AD28" s="8"/>
@@ -4761,74 +4924,89 @@
       <c r="A29" s="52">
         <v>27</v>
       </c>
-      <c r="B29" s="83"/>
-      <c r="C29" s="191" t="s">
+      <c r="B29" s="168"/>
+      <c r="C29" s="95" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="87" t="s">
+        <v>143</v>
+      </c>
+      <c r="E29" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="192"/>
-      <c r="E29" s="192" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="193" t="s">
-        <v>145</v>
-      </c>
-      <c r="G29" s="194" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" s="195"/>
-      <c r="I29" s="194" t="s">
-        <v>245</v>
-      </c>
-      <c r="J29" s="194"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="128">
+      <c r="G29" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" s="66" t="s">
+        <v>276</v>
+      </c>
+      <c r="I29" s="66" t="s">
+        <v>277</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="K29" s="11">
+        <v>100</v>
+      </c>
+      <c r="L29" s="118">
         <v>1</v>
       </c>
-      <c r="M29" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N29" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O29" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P29" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q29" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R29" s="17"/>
-      <c r="S29" s="57"/>
+      <c r="M29" s="11">
+        <v>100</v>
+      </c>
+      <c r="N29" s="11">
+        <v>100</v>
+      </c>
+      <c r="O29" s="11">
+        <v>600</v>
+      </c>
+      <c r="P29" s="11">
+        <v>1100</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>10500</v>
+      </c>
+      <c r="R29" s="127" t="s">
+        <v>15</v>
+      </c>
+      <c r="S29" s="57">
+        <v>2.2000000000000001E-3</v>
+      </c>
       <c r="T29" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="57"/>
+        <v>0.22</v>
+      </c>
+      <c r="U29" s="57">
+        <v>2.2000000000000001E-3</v>
+      </c>
       <c r="V29" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W29" s="13"/>
-      <c r="X29" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="W29" s="13">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="X29" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="6">
+        <v>1.32</v>
+      </c>
+      <c r="Y29" s="13">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="Z29" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA29" s="13"/>
-      <c r="AB29" s="6">
+        <v>1.8699999999999999</v>
+      </c>
+      <c r="AA29" s="13">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="AB29" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="AC29" s="14"/>
       <c r="AD29" s="8"/>
@@ -4838,72 +5016,89 @@
       <c r="A30" s="52">
         <v>28</v>
       </c>
-      <c r="B30" s="83"/>
-      <c r="C30" s="107" t="s">
+      <c r="B30" s="168"/>
+      <c r="C30" s="97" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="87" t="s">
         <v>146</v>
       </c>
-      <c r="D30" s="94" t="s">
+      <c r="E30" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="E30" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="128">
+      <c r="G30" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="66" t="s">
+        <v>278</v>
+      </c>
+      <c r="I30" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="K30" s="11">
+        <v>100</v>
+      </c>
+      <c r="L30" s="118">
         <v>1</v>
       </c>
-      <c r="M30" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N30" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O30" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P30" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q30" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R30" s="17"/>
-      <c r="S30" s="57"/>
+      <c r="M30" s="11">
+        <v>100</v>
+      </c>
+      <c r="N30" s="11">
+        <v>100</v>
+      </c>
+      <c r="O30" s="11">
+        <v>600</v>
+      </c>
+      <c r="P30" s="11">
+        <v>1100</v>
+      </c>
+      <c r="Q30" s="11">
+        <v>10500</v>
+      </c>
+      <c r="R30" s="127" t="s">
+        <v>15</v>
+      </c>
+      <c r="S30" s="57">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="T30" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="57"/>
+        <v>0.12</v>
+      </c>
+      <c r="U30" s="57">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="V30" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W30" s="13"/>
-      <c r="X30" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="W30" s="13">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="X30" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="13"/>
-      <c r="Z30" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="Y30" s="13">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Z30" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA30" s="13"/>
-      <c r="AB30" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="AA30" s="13">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="AB30" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC30" s="14"/>
       <c r="AD30" s="8"/>
@@ -4913,74 +5108,89 @@
       <c r="A31" s="52">
         <v>29</v>
       </c>
-      <c r="B31" s="83"/>
-      <c r="C31" s="102" t="s">
+      <c r="B31" s="168"/>
+      <c r="C31" s="95" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="103" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="94" t="s">
+      <c r="E31" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E31" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="16" t="s">
+      <c r="G31" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="G31" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H31" s="66"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="128">
-        <v>1</v>
-      </c>
-      <c r="M31" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N31" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O31" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P31" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q31" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R31" s="12"/>
-      <c r="S31" s="57"/>
+      <c r="H31" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="I31" s="78" t="s">
+        <v>285</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="K31" s="11">
+        <v>100</v>
+      </c>
+      <c r="L31" s="118">
+        <v>6</v>
+      </c>
+      <c r="M31" s="11">
+        <v>100</v>
+      </c>
+      <c r="N31" s="11">
+        <v>200</v>
+      </c>
+      <c r="O31" s="11">
+        <v>3200</v>
+      </c>
+      <c r="P31" s="11">
+        <v>6400</v>
+      </c>
+      <c r="Q31" s="11">
+        <v>62000</v>
+      </c>
+      <c r="R31" s="127" t="s">
+        <v>15</v>
+      </c>
+      <c r="S31" s="57">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="T31" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="57"/>
+        <v>0.12</v>
+      </c>
+      <c r="U31" s="57">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="V31" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W31" s="13"/>
-      <c r="X31" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="W31" s="13">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="X31" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="13"/>
-      <c r="Z31" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="Y31" s="13">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Z31" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA31" s="13"/>
-      <c r="AB31" s="6">
+        <v>5.76</v>
+      </c>
+      <c r="AA31" s="13">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="AB31" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49.6</v>
       </c>
       <c r="AC31" s="14"/>
       <c r="AD31" s="8"/>
@@ -4990,72 +5200,89 @@
       <c r="A32" s="52">
         <v>30</v>
       </c>
-      <c r="B32" s="83"/>
-      <c r="C32" s="107" t="s">
+      <c r="B32" s="168"/>
+      <c r="C32" s="95" t="s">
         <v>152</v>
       </c>
-      <c r="D32" s="94" t="s">
+      <c r="D32" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="E32" s="92" t="s">
-        <v>55</v>
+      <c r="E32" s="85" t="s">
+        <v>54</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="67"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="128">
+      <c r="G32" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" s="66" t="s">
+        <v>287</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="K32" s="11">
+        <v>50</v>
+      </c>
+      <c r="L32" s="118">
         <v>1</v>
       </c>
-      <c r="M32" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N32" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O32" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P32" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q32" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R32" s="12"/>
-      <c r="S32" s="57"/>
+      <c r="M32" s="11">
+        <v>50</v>
+      </c>
+      <c r="N32" s="11">
+        <v>50</v>
+      </c>
+      <c r="O32" s="11">
+        <v>550</v>
+      </c>
+      <c r="P32" s="11">
+        <v>1100</v>
+      </c>
+      <c r="Q32" s="11">
+        <v>10500</v>
+      </c>
+      <c r="R32" s="127" t="s">
+        <v>15</v>
+      </c>
+      <c r="S32" s="57">
+        <v>8.6E-3</v>
+      </c>
       <c r="T32" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="57"/>
+        <v>0.43</v>
+      </c>
+      <c r="U32" s="57">
+        <v>8.6E-3</v>
+      </c>
       <c r="V32" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="13"/>
-      <c r="X32" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="W32" s="13">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="X32" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="13"/>
-      <c r="Z32" s="6">
+        <v>3.5749999999999997</v>
+      </c>
+      <c r="Y32" s="13">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="Z32" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA32" s="13"/>
-      <c r="AB32" s="6">
+        <v>7.1499999999999995</v>
+      </c>
+      <c r="AA32" s="13">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="AB32" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>53.550000000000004</v>
       </c>
       <c r="AC32" s="14"/>
       <c r="AD32" s="8"/>
@@ -5065,74 +5292,89 @@
       <c r="A33" s="52">
         <v>31</v>
       </c>
-      <c r="B33" s="83"/>
-      <c r="C33" s="102" t="s">
+      <c r="B33" s="168"/>
+      <c r="C33" s="97" t="s">
         <v>155</v>
       </c>
-      <c r="D33" s="113" t="s">
+      <c r="D33" s="87" t="s">
         <v>156</v>
       </c>
-      <c r="E33" s="92" t="s">
-        <v>55</v>
+      <c r="E33" s="85" t="s">
+        <v>54</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>157</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H33" s="66"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="128">
-        <v>6</v>
-      </c>
-      <c r="M33" s="4">
-        <f t="shared" si="5"/>
-        <v>69</v>
-      </c>
-      <c r="N33" s="4">
-        <f t="shared" si="6"/>
-        <v>138</v>
-      </c>
-      <c r="O33" s="4">
-        <f t="shared" si="7"/>
-        <v>3450</v>
-      </c>
-      <c r="P33" s="4">
-        <f t="shared" si="8"/>
-        <v>6900</v>
-      </c>
-      <c r="Q33" s="4">
-        <f t="shared" si="9"/>
-        <v>69000</v>
-      </c>
-      <c r="R33" s="12"/>
-      <c r="S33" s="57"/>
+        <v>240</v>
+      </c>
+      <c r="H33" s="66" t="s">
+        <v>290</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="K33" s="68">
+        <v>100</v>
+      </c>
+      <c r="L33" s="118">
+        <v>3</v>
+      </c>
+      <c r="M33" s="11">
+        <v>100</v>
+      </c>
+      <c r="N33" s="11">
+        <v>100</v>
+      </c>
+      <c r="O33" s="11">
+        <v>1600</v>
+      </c>
+      <c r="P33" s="11">
+        <v>3200</v>
+      </c>
+      <c r="Q33" s="11">
+        <v>31000</v>
+      </c>
+      <c r="R33" s="127" t="s">
+        <v>15</v>
+      </c>
+      <c r="S33" s="57">
+        <v>1.2999999999999999E-3</v>
+      </c>
       <c r="T33" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="57"/>
+        <v>0.13</v>
+      </c>
+      <c r="U33" s="57">
+        <v>1.2999999999999999E-3</v>
+      </c>
       <c r="V33" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="13"/>
-      <c r="X33" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="W33" s="13">
+        <v>1E-3</v>
+      </c>
+      <c r="X33" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="13"/>
-      <c r="Z33" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="Y33" s="13">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Z33" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA33" s="13"/>
-      <c r="AB33" s="6">
+        <v>2.56</v>
+      </c>
+      <c r="AA33" s="13">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="AB33" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="AC33" s="14"/>
       <c r="AD33" s="8"/>
@@ -5142,76 +5384,91 @@
       <c r="A34" s="52">
         <v>32</v>
       </c>
-      <c r="B34" s="83"/>
-      <c r="C34" s="102" t="s">
+      <c r="B34" s="168"/>
+      <c r="C34" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="87" t="s">
         <v>159</v>
       </c>
-      <c r="D34" s="94" t="s">
+      <c r="E34" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="F34" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="E34" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>161</v>
-      </c>
       <c r="G34" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" s="66"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="128">
-        <v>1</v>
-      </c>
-      <c r="M34" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N34" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O34" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P34" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q34" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R34" s="12"/>
-      <c r="S34" s="57"/>
+        <v>270</v>
+      </c>
+      <c r="H34" s="66" t="s">
+        <v>292</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="K34" s="68">
+        <v>50</v>
+      </c>
+      <c r="L34" s="118">
+        <v>4</v>
+      </c>
+      <c r="M34" s="11">
+        <v>50</v>
+      </c>
+      <c r="N34" s="11">
+        <v>100</v>
+      </c>
+      <c r="O34" s="11">
+        <v>2100</v>
+      </c>
+      <c r="P34" s="11">
+        <v>4200</v>
+      </c>
+      <c r="Q34" s="11">
+        <v>41500</v>
+      </c>
+      <c r="R34" s="129" t="s">
+        <v>15</v>
+      </c>
+      <c r="S34" s="130">
+        <v>9.2999999999999992E-3</v>
+      </c>
       <c r="T34" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U34" s="57"/>
+        <v>0.46499999999999997</v>
+      </c>
+      <c r="U34" s="130">
+        <v>9.2999999999999992E-3</v>
+      </c>
       <c r="V34" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W34" s="13"/>
-      <c r="X34" s="6">
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="W34" s="60">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="X34" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="13"/>
-      <c r="Z34" s="6">
+        <v>14.28</v>
+      </c>
+      <c r="Y34" s="60">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="Z34" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA34" s="13"/>
-      <c r="AB34" s="6">
+        <v>28.56</v>
+      </c>
+      <c r="AA34" s="60">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="AB34" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC34" s="14"/>
+        <v>257.3</v>
+      </c>
+      <c r="AC34" s="18"/>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
     </row>
@@ -5219,74 +5476,91 @@
       <c r="A35" s="52">
         <v>33</v>
       </c>
-      <c r="B35" s="83"/>
-      <c r="C35" s="107" t="s">
+      <c r="B35" s="169"/>
+      <c r="C35" s="104" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="105" t="s">
         <v>162</v>
       </c>
-      <c r="D35" s="94" t="s">
+      <c r="E35" s="92" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="E35" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="68"/>
-      <c r="L35" s="128">
-        <v>3</v>
-      </c>
-      <c r="M35" s="4">
-        <f t="shared" si="5"/>
-        <v>35</v>
-      </c>
-      <c r="N35" s="4">
-        <f t="shared" si="6"/>
-        <v>69</v>
-      </c>
-      <c r="O35" s="4">
-        <f t="shared" si="7"/>
-        <v>1725</v>
-      </c>
-      <c r="P35" s="4">
-        <f t="shared" si="8"/>
-        <v>3450</v>
-      </c>
-      <c r="Q35" s="4">
-        <f t="shared" si="9"/>
-        <v>34500</v>
-      </c>
-      <c r="R35" s="12"/>
-      <c r="S35" s="57"/>
-      <c r="T35" s="13">
+      <c r="G35" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H35" s="131" t="s">
+        <v>294</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="K35" s="71">
+        <v>5</v>
+      </c>
+      <c r="L35" s="119">
+        <v>1</v>
+      </c>
+      <c r="M35" s="23">
+        <v>10</v>
+      </c>
+      <c r="N35" s="23">
+        <v>25</v>
+      </c>
+      <c r="O35" s="23">
+        <v>525</v>
+      </c>
+      <c r="P35" s="23">
+        <v>1050</v>
+      </c>
+      <c r="Q35" s="23">
+        <v>10500</v>
+      </c>
+      <c r="R35" s="162" t="s">
+        <v>15</v>
+      </c>
+      <c r="S35" s="61">
+        <v>9.4399999999999998E-2</v>
+      </c>
+      <c r="T35" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U35" s="57"/>
-      <c r="V35" s="13">
+        <v>0.94399999999999995</v>
+      </c>
+      <c r="U35" s="61">
+        <v>9.4399999999999998E-2</v>
+      </c>
+      <c r="V35" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W35" s="13"/>
-      <c r="X35" s="6">
+        <v>2.36</v>
+      </c>
+      <c r="W35" s="25">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="X35" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="13"/>
-      <c r="Z35" s="6">
+        <v>33.862500000000004</v>
+      </c>
+      <c r="Y35" s="25">
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="Z35" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA35" s="13"/>
-      <c r="AB35" s="6">
+        <v>67.725000000000009</v>
+      </c>
+      <c r="AA35" s="25">
+        <v>6.1899999999999997E-2</v>
+      </c>
+      <c r="AB35" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC35" s="14"/>
+        <v>649.94999999999993</v>
+      </c>
+      <c r="AC35" s="26"/>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
     </row>
@@ -5294,74 +5568,93 @@
       <c r="A36" s="52">
         <v>34</v>
       </c>
-      <c r="B36" s="83"/>
-      <c r="C36" s="107" t="s">
+      <c r="B36" s="167" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="94" t="s">
         <v>165</v>
       </c>
-      <c r="D36" s="94" t="s">
+      <c r="D36" s="82" t="s">
         <v>166</v>
       </c>
-      <c r="E36" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="F36" s="16" t="s">
+      <c r="E36" s="82" t="s">
         <v>167</v>
       </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="128">
-        <v>4</v>
+      <c r="F36" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="H36" s="76" t="s">
+        <v>297</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K36" s="132">
+        <v>10</v>
+      </c>
+      <c r="L36" s="3">
+        <v>1</v>
       </c>
       <c r="M36" s="4">
-        <f t="shared" si="5"/>
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N36" s="4">
-        <f t="shared" si="6"/>
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="O36" s="4">
-        <f t="shared" si="7"/>
-        <v>2300</v>
+        <v>520</v>
       </c>
       <c r="P36" s="4">
-        <f t="shared" si="8"/>
-        <v>4600</v>
+        <v>1050</v>
       </c>
       <c r="Q36" s="4">
-        <f t="shared" si="9"/>
-        <v>46000</v>
-      </c>
-      <c r="R36" s="141"/>
-      <c r="S36" s="142"/>
-      <c r="T36" s="13">
+        <v>10200</v>
+      </c>
+      <c r="R36" s="163" t="s">
+        <v>15</v>
+      </c>
+      <c r="S36" s="56">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="T36" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U36" s="142"/>
-      <c r="V36" s="13">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="U36" s="56">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="V36" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="60"/>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.04</v>
+      </c>
       <c r="X36" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="60"/>
+        <v>20.8</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>3.7400000000000003E-2</v>
+      </c>
       <c r="Z36" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA36" s="60"/>
+        <v>39.270000000000003</v>
+      </c>
+      <c r="AA36" s="6">
+        <v>3.5799999999999998E-2</v>
+      </c>
       <c r="AB36" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC36" s="18"/>
+        <v>365.15999999999997</v>
+      </c>
+      <c r="AC36" s="7"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
     </row>
@@ -5369,76 +5662,91 @@
       <c r="A37" s="52">
         <v>35</v>
       </c>
-      <c r="B37" s="85"/>
-      <c r="C37" s="114" t="s">
-        <v>168</v>
-      </c>
-      <c r="D37" s="115" t="s">
+      <c r="B37" s="169"/>
+      <c r="C37" s="96" t="s">
         <v>169</v>
       </c>
-      <c r="E37" s="99" t="s">
-        <v>143</v>
+      <c r="D37" s="92" t="s">
+        <v>170</v>
+      </c>
+      <c r="E37" s="92" t="s">
+        <v>171</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H37" s="143"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="71"/>
-      <c r="L37" s="129">
+        <v>298</v>
+      </c>
+      <c r="H37" s="131" t="s">
+        <v>299</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="K37" s="71">
+        <v>5</v>
+      </c>
+      <c r="L37" s="21">
         <v>1</v>
       </c>
-      <c r="M37" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N37" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O37" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P37" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q37" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R37" s="24"/>
-      <c r="S37" s="61"/>
-      <c r="T37" s="13">
+      <c r="M37" s="23">
+        <v>10</v>
+      </c>
+      <c r="N37" s="23">
+        <v>25</v>
+      </c>
+      <c r="O37" s="23">
+        <v>520</v>
+      </c>
+      <c r="P37" s="23">
+        <v>1050</v>
+      </c>
+      <c r="Q37" s="23">
+        <v>10500</v>
+      </c>
+      <c r="R37" s="172" t="s">
+        <v>15</v>
+      </c>
+      <c r="S37" s="151">
+        <v>0.1308</v>
+      </c>
+      <c r="T37" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="61"/>
-      <c r="V37" s="13">
+        <v>1.3080000000000001</v>
+      </c>
+      <c r="U37" s="151">
+        <v>0.1308</v>
+      </c>
+      <c r="V37" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="25"/>
-      <c r="X37" s="6">
+        <v>3.27</v>
+      </c>
+      <c r="W37" s="152">
+        <v>8.2100000000000006E-2</v>
+      </c>
+      <c r="X37" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="25"/>
-      <c r="Z37" s="6">
+        <v>42.692</v>
+      </c>
+      <c r="Y37" s="152">
+        <v>8.2100000000000006E-2</v>
+      </c>
+      <c r="Z37" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA37" s="25"/>
-      <c r="AB37" s="6">
+        <v>86.205000000000013</v>
+      </c>
+      <c r="AA37" s="152">
+        <v>8.2100000000000006E-2</v>
+      </c>
+      <c r="AB37" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC37" s="26"/>
+        <v>862.05000000000007</v>
+      </c>
+      <c r="AC37" s="153"/>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
     </row>
@@ -5446,76 +5754,78 @@
       <c r="A38" s="52">
         <v>36</v>
       </c>
-      <c r="B38" s="84" t="s">
-        <v>171</v>
-      </c>
-      <c r="C38" s="101" t="s">
-        <v>172</v>
-      </c>
-      <c r="D38" s="89" t="s">
+      <c r="B38" s="79" t="s">
         <v>173</v>
       </c>
-      <c r="E38" s="89" t="s">
+      <c r="C38" s="193" t="s">
         <v>174</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="D38" s="101" t="s">
         <v>175</v>
       </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="144"/>
-      <c r="L38" s="3">
+      <c r="E38" s="101" t="s">
+        <v>176</v>
+      </c>
+      <c r="F38" s="101" t="s">
+        <v>177</v>
+      </c>
+      <c r="G38" s="102" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="166"/>
+      <c r="I38" s="194"/>
+      <c r="J38" s="194"/>
+      <c r="K38" s="195"/>
+      <c r="L38" s="121">
         <v>1</v>
       </c>
-      <c r="M38" s="4">
+      <c r="M38" s="140">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="N38" s="4">
+      <c r="N38" s="140">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="O38" s="4">
+      <c r="O38" s="140">
         <f t="shared" si="7"/>
         <v>575</v>
       </c>
-      <c r="P38" s="4">
+      <c r="P38" s="140">
         <f t="shared" si="8"/>
         <v>1150</v>
       </c>
-      <c r="Q38" s="4">
+      <c r="Q38" s="140">
         <f t="shared" si="9"/>
         <v>11500</v>
       </c>
-      <c r="R38" s="145"/>
-      <c r="S38" s="56"/>
-      <c r="T38" s="13">
+      <c r="R38" s="196"/>
+      <c r="S38" s="141"/>
+      <c r="T38" s="142">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U38" s="56"/>
-      <c r="V38" s="13">
+      <c r="U38" s="141"/>
+      <c r="V38" s="142">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6">
+      <c r="W38" s="142"/>
+      <c r="X38" s="142">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y38" s="6"/>
-      <c r="Z38" s="6">
+      <c r="Y38" s="142"/>
+      <c r="Z38" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA38" s="6"/>
-      <c r="AB38" s="6">
+      <c r="AA38" s="142"/>
+      <c r="AB38" s="142">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC38" s="7"/>
+      <c r="AC38" s="197"/>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
     </row>
@@ -5523,74 +5833,93 @@
       <c r="A39" s="52">
         <v>37</v>
       </c>
-      <c r="B39" s="85"/>
-      <c r="C39" s="103" t="s">
-        <v>176</v>
-      </c>
-      <c r="D39" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="E39" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="F39" s="22" t="s">
+      <c r="B39" s="167" t="s">
         <v>179</v>
       </c>
-      <c r="G39" s="20"/>
-      <c r="H39" s="143"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="21">
+      <c r="C39" s="94" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="106" t="s">
+        <v>181</v>
+      </c>
+      <c r="F39" s="107" t="s">
+        <v>182</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="H39" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="K39" s="150">
+        <v>10</v>
+      </c>
+      <c r="L39" s="122">
         <v>1</v>
       </c>
       <c r="M39" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N39" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O39" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
+        <v>530</v>
       </c>
       <c r="P39" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
+        <v>1050</v>
       </c>
       <c r="Q39" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R39" s="165"/>
-      <c r="S39" s="166"/>
-      <c r="T39" s="13">
+        <v>10200</v>
+      </c>
+      <c r="R39" s="163" t="s">
+        <v>15</v>
+      </c>
+      <c r="S39" s="56">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="T39" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U39" s="166"/>
-      <c r="V39" s="13">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="U39" s="56">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="V39" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W39" s="167"/>
+        <v>1.208</v>
+      </c>
+      <c r="W39" s="6">
+        <v>4.2799999999999998E-2</v>
+      </c>
       <c r="X39" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="167"/>
+        <v>22.683999999999997</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>4.0099999999999997E-2</v>
+      </c>
       <c r="Z39" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA39" s="167"/>
+        <v>42.104999999999997</v>
+      </c>
+      <c r="AA39" s="6">
+        <v>3.8300000000000001E-2</v>
+      </c>
       <c r="AB39" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC39" s="168"/>
+        <v>390.66</v>
+      </c>
+      <c r="AC39" s="29"/>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
     </row>
@@ -5598,78 +5927,92 @@
       <c r="A40" s="52">
         <v>38</v>
       </c>
-      <c r="B40" s="104" t="s">
-        <v>180</v>
-      </c>
-      <c r="C40" s="174" t="s">
-        <v>181</v>
-      </c>
-      <c r="D40" s="105" t="s">
-        <v>182</v>
-      </c>
-      <c r="E40" s="105" t="s">
+      <c r="B40" s="168"/>
+      <c r="C40" s="97" t="s">
         <v>183</v>
       </c>
-      <c r="F40" s="105" t="s">
+      <c r="D40" s="108" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="108" t="s">
         <v>184</v>
       </c>
-      <c r="G40" s="106" t="s">
+      <c r="F40" s="109" t="s">
         <v>185</v>
       </c>
-      <c r="H40" s="175"/>
-      <c r="I40" s="176"/>
-      <c r="J40" s="176"/>
-      <c r="K40" s="177"/>
-      <c r="L40" s="130">
+      <c r="G40" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K40" s="36">
         <v>1</v>
       </c>
-      <c r="M40" s="4">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="N40" s="4">
-        <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="O40" s="4">
-        <f t="shared" si="7"/>
-        <v>575</v>
-      </c>
-      <c r="P40" s="4">
-        <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="Q40" s="4">
-        <f t="shared" si="9"/>
-        <v>11500</v>
-      </c>
-      <c r="R40" s="178"/>
-      <c r="S40" s="179"/>
+      <c r="L40" s="123">
+        <v>1</v>
+      </c>
+      <c r="M40" s="11">
+        <v>11</v>
+      </c>
+      <c r="N40" s="11">
+        <f t="shared" ref="N40:N45" si="10">ROUND(L40*20*1.11,0)</f>
+        <v>22</v>
+      </c>
+      <c r="O40" s="11">
+        <v>520</v>
+      </c>
+      <c r="P40" s="11">
+        <v>1050</v>
+      </c>
+      <c r="Q40" s="11">
+        <v>10200</v>
+      </c>
+      <c r="R40" s="159" t="s">
+        <v>15</v>
+      </c>
+      <c r="S40" s="57">
+        <v>0.28439999999999999</v>
+      </c>
       <c r="T40" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U40" s="179"/>
+        <v>3.1284000000000001</v>
+      </c>
+      <c r="U40" s="57">
+        <v>0.28439999999999999</v>
+      </c>
       <c r="V40" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W40" s="180"/>
-      <c r="X40" s="6">
+        <v>6.2568000000000001</v>
+      </c>
+      <c r="W40" s="13">
+        <v>0.245</v>
+      </c>
+      <c r="X40" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="180"/>
-      <c r="Z40" s="6">
+        <v>127.39999999999999</v>
+      </c>
+      <c r="Y40" s="13">
+        <v>0.24160000000000001</v>
+      </c>
+      <c r="Z40" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA40" s="180"/>
-      <c r="AB40" s="6">
+        <v>253.68</v>
+      </c>
+      <c r="AA40" s="13">
+        <v>0.24160000000000001</v>
+      </c>
+      <c r="AB40" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC40" s="181"/>
+        <v>2464.3200000000002</v>
+      </c>
+      <c r="AC40" s="14"/>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
     </row>
@@ -5677,76 +6020,93 @@
       <c r="A41" s="52">
         <v>39</v>
       </c>
-      <c r="B41" s="84" t="s">
+      <c r="B41" s="168"/>
+      <c r="C41" s="97" t="s">
         <v>186</v>
       </c>
-      <c r="C41" s="101" t="s">
+      <c r="D41" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" s="108" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="116" t="s">
-        <v>36</v>
-      </c>
-      <c r="E41" s="116" t="s">
+      <c r="F41" s="109" t="s">
         <v>188</v>
       </c>
-      <c r="F41" s="117" t="s">
-        <v>189</v>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="164"/>
-      <c r="L41" s="133">
+      <c r="G41" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>305</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K41" s="36">
         <v>1</v>
       </c>
-      <c r="M41" s="4">
-        <f>ROUND(L41*10*1.11, 0)</f>
+      <c r="L41" s="123">
+        <v>1</v>
+      </c>
+      <c r="M41" s="11">
+        <f t="shared" ref="M41:M45" si="11">ROUND(L41*10*1.11, 0)</f>
         <v>11</v>
       </c>
-      <c r="N41" s="4">
-        <f>ROUND(L41*20*1.11,0)</f>
+      <c r="N41" s="11">
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
-      <c r="O41" s="4">
-        <f>ROUND(L41*500*1.11,0)</f>
-        <v>555</v>
-      </c>
-      <c r="P41" s="4">
-        <f>ROUND(L41*1000*1.11,0)</f>
-        <v>1110</v>
-      </c>
-      <c r="Q41" s="4">
-        <f>ROUND(L41*10000*1.11,0)</f>
-        <v>11100</v>
-      </c>
-      <c r="R41" s="145"/>
-      <c r="S41" s="56"/>
+      <c r="O41" s="11">
+        <v>520</v>
+      </c>
+      <c r="P41" s="11">
+        <v>1050</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>10200</v>
+      </c>
+      <c r="R41" s="159" t="s">
+        <v>15</v>
+      </c>
+      <c r="S41" s="57">
+        <v>0.16830000000000001</v>
+      </c>
       <c r="T41" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U41" s="56"/>
+        <v>1.8513000000000002</v>
+      </c>
+      <c r="U41" s="57">
+        <v>0.16830000000000001</v>
+      </c>
       <c r="V41" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W41" s="6"/>
-      <c r="X41" s="6">
+        <v>3.7026000000000003</v>
+      </c>
+      <c r="W41" s="13">
+        <v>0.14480000000000001</v>
+      </c>
+      <c r="X41" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="6">
+        <v>75.296000000000006</v>
+      </c>
+      <c r="Y41" s="13">
+        <v>0.14269999999999999</v>
+      </c>
+      <c r="Z41" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA41" s="6"/>
-      <c r="AB41" s="6">
+        <v>149.83499999999998</v>
+      </c>
+      <c r="AA41" s="13">
+        <v>0.14269999999999999</v>
+      </c>
+      <c r="AB41" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC41" s="29"/>
+        <v>1455.54</v>
+      </c>
+      <c r="AC41" s="14"/>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
     </row>
@@ -5754,70 +6114,87 @@
       <c r="A42" s="52">
         <v>40</v>
       </c>
-      <c r="B42" s="83"/>
-      <c r="C42" s="107" t="s">
+      <c r="B42" s="168"/>
+      <c r="C42" s="95" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="108" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="108" t="s">
+        <v>181</v>
+      </c>
+      <c r="F42" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="D42" s="118" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" s="118" t="s">
+      <c r="G42" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="F42" s="119" t="s">
-        <v>192</v>
-      </c>
-      <c r="G42" s="34"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="134">
+      <c r="H42" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K42" s="36">
+        <v>10</v>
+      </c>
+      <c r="L42" s="123">
         <v>1</v>
       </c>
-      <c r="M42" s="4">
-        <f t="shared" ref="M42:M48" si="10">ROUND(L42*10*1.11, 0)</f>
+      <c r="M42" s="11">
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
-      <c r="N42" s="4">
-        <f t="shared" ref="N42:N48" si="11">ROUND(L42*20*1.11,0)</f>
+      <c r="N42" s="11">
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
-      <c r="O42" s="4">
-        <f t="shared" ref="O42:O48" si="12">ROUND(L42*500*1.11,0)</f>
-        <v>555</v>
-      </c>
-      <c r="P42" s="4">
-        <f t="shared" ref="P42:P48" si="13">ROUND(L42*1000*1.11,0)</f>
+      <c r="O42" s="11">
+        <v>520</v>
+      </c>
+      <c r="P42" s="11">
+        <f t="shared" ref="P42:P45" si="12">ROUND(L42*1000*1.11,0)</f>
         <v>1110</v>
       </c>
-      <c r="Q42" s="4">
-        <f t="shared" ref="Q42:Q48" si="14">ROUND(L42*10000*1.11,0)</f>
+      <c r="Q42" s="11">
+        <f t="shared" ref="Q42:Q45" si="13">ROUND(L42*10000*1.11,0)</f>
         <v>11100</v>
       </c>
-      <c r="R42" s="17"/>
-      <c r="S42" s="57"/>
+      <c r="R42" s="159" t="s">
+        <v>316</v>
+      </c>
+      <c r="S42" s="57">
+        <v>1.0900000000000001</v>
+      </c>
       <c r="T42" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U42" s="57"/>
+        <v>11.99</v>
+      </c>
+      <c r="U42" s="57">
+        <v>0.85</v>
+      </c>
       <c r="V42" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W42" s="13"/>
-      <c r="X42" s="6">
+        <v>18.7</v>
+      </c>
+      <c r="W42" s="13">
+        <v>0.890384615384615</v>
+      </c>
+      <c r="X42" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>462.99999999999977</v>
       </c>
       <c r="Y42" s="13"/>
-      <c r="Z42" s="6">
+      <c r="Z42" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA42" s="13"/>
-      <c r="AB42" s="6">
+      <c r="AB42" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5829,70 +6206,87 @@
       <c r="A43" s="52">
         <v>41</v>
       </c>
-      <c r="B43" s="83"/>
-      <c r="C43" s="107" t="s">
+      <c r="B43" s="168"/>
+      <c r="C43" s="95" t="s">
+        <v>192</v>
+      </c>
+      <c r="D43" s="108" t="s">
         <v>193</v>
       </c>
-      <c r="D43" s="118" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" s="118" t="s">
+      <c r="E43" s="108" t="s">
         <v>194</v>
       </c>
-      <c r="F43" s="119" t="s">
+      <c r="F43" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="G43" s="34"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="134">
+      <c r="G43" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="H43" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K43" s="11">
+        <v>10</v>
+      </c>
+      <c r="L43" s="123">
         <v>1</v>
       </c>
-      <c r="M43" s="4">
+      <c r="M43" s="11">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="N43" s="11">
         <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="N43" s="4">
-        <f t="shared" si="11"/>
         <v>22</v>
       </c>
-      <c r="O43" s="4">
-        <f t="shared" si="12"/>
-        <v>555</v>
-      </c>
-      <c r="P43" s="4">
-        <f t="shared" si="13"/>
-        <v>1110</v>
-      </c>
-      <c r="Q43" s="4">
-        <f t="shared" si="14"/>
-        <v>11100</v>
-      </c>
-      <c r="R43" s="17"/>
-      <c r="S43" s="57"/>
+      <c r="O43" s="11">
+        <v>520</v>
+      </c>
+      <c r="P43" s="11">
+        <v>1050</v>
+      </c>
+      <c r="Q43" s="11">
+        <v>10200</v>
+      </c>
+      <c r="R43" s="127" t="s">
+        <v>316</v>
+      </c>
+      <c r="S43" s="57">
+        <v>2.5030000000000001</v>
+      </c>
       <c r="T43" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U43" s="57"/>
+        <v>27.533000000000001</v>
+      </c>
+      <c r="U43" s="57">
+        <v>2.2113636363636302</v>
+      </c>
       <c r="V43" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W43" s="13"/>
-      <c r="X43" s="6">
+        <v>48.649999999999864</v>
+      </c>
+      <c r="W43" s="13">
+        <v>1.9238846153846101</v>
+      </c>
+      <c r="X43" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="13"/>
-      <c r="Z43" s="6">
+        <v>1000.4199999999972</v>
+      </c>
+      <c r="Y43" s="13">
+        <v>1.9</v>
+      </c>
+      <c r="Z43" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1995</v>
       </c>
       <c r="AA43" s="13"/>
-      <c r="AB43" s="6">
+      <c r="AB43" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5904,74 +6298,91 @@
       <c r="A44" s="52">
         <v>42</v>
       </c>
-      <c r="B44" s="83"/>
-      <c r="C44" s="102" t="s">
+      <c r="B44" s="168"/>
+      <c r="C44" s="97" t="s">
         <v>196</v>
       </c>
-      <c r="D44" s="118" t="s">
-        <v>39</v>
-      </c>
-      <c r="E44" s="118" t="s">
-        <v>188</v>
-      </c>
-      <c r="F44" s="119" t="s">
+      <c r="D44" s="108" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="108" t="s">
         <v>197</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="F44" s="109" t="s">
         <v>198</v>
       </c>
-      <c r="H44" s="35"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="134">
+      <c r="G44" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K44" s="11">
         <v>1</v>
       </c>
-      <c r="M44" s="4">
+      <c r="L44" s="123">
+        <v>1</v>
+      </c>
+      <c r="M44" s="11">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="N44" s="11">
         <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="N44" s="4">
-        <f t="shared" si="11"/>
         <v>22</v>
       </c>
-      <c r="O44" s="4">
-        <f t="shared" si="12"/>
-        <v>555</v>
-      </c>
-      <c r="P44" s="4">
-        <f t="shared" si="13"/>
-        <v>1110</v>
-      </c>
-      <c r="Q44" s="4">
-        <f t="shared" si="14"/>
-        <v>11100</v>
-      </c>
-      <c r="R44" s="17"/>
-      <c r="S44" s="57"/>
+      <c r="O44" s="11">
+        <v>510</v>
+      </c>
+      <c r="P44" s="11">
+        <v>1020</v>
+      </c>
+      <c r="Q44" s="11">
+        <v>10100</v>
+      </c>
+      <c r="R44" s="127" t="s">
+        <v>15</v>
+      </c>
+      <c r="S44" s="57">
+        <v>3.8121999999999998</v>
+      </c>
       <c r="T44" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U44" s="57"/>
+        <v>41.934199999999997</v>
+      </c>
+      <c r="U44" s="58">
+        <v>3.8121999999999998</v>
+      </c>
       <c r="V44" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W44" s="13"/>
-      <c r="X44" s="6">
+        <v>83.868399999999994</v>
+      </c>
+      <c r="W44" s="13">
+        <v>3.044</v>
+      </c>
+      <c r="X44" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="13"/>
-      <c r="Z44" s="6">
+        <v>1552.44</v>
+      </c>
+      <c r="Y44" s="13">
+        <v>3.0169000000000001</v>
+      </c>
+      <c r="Z44" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA44" s="13"/>
-      <c r="AB44" s="6">
+        <v>3077.2380000000003</v>
+      </c>
+      <c r="AA44" s="13">
+        <v>3.0169000000000001</v>
+      </c>
+      <c r="AB44" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30470.690000000002</v>
       </c>
       <c r="AC44" s="14"/>
       <c r="AD44" s="8"/>
@@ -5981,47 +6392,47 @@
       <c r="A45" s="52">
         <v>43</v>
       </c>
-      <c r="B45" s="83"/>
-      <c r="C45" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="D45" s="118" t="s">
+      <c r="B45" s="168"/>
+      <c r="C45" s="110" t="s">
         <v>200</v>
       </c>
-      <c r="E45" s="118" t="s">
+      <c r="D45" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="111" t="s">
         <v>201</v>
       </c>
-      <c r="F45" s="119" t="s">
+      <c r="F45" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="G45" s="34" t="s">
-        <v>198</v>
+      <c r="G45" s="9" t="s">
+        <v>191</v>
       </c>
       <c r="H45" s="30"/>
       <c r="I45" s="9"/>
       <c r="J45" s="9"/>
       <c r="K45" s="11"/>
-      <c r="L45" s="134">
+      <c r="L45" s="10">
         <v>1</v>
       </c>
-      <c r="M45" s="4">
+      <c r="M45" s="11">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="N45" s="11">
         <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="N45" s="4">
-        <f t="shared" si="11"/>
         <v>22</v>
       </c>
-      <c r="O45" s="4">
+      <c r="O45" s="11">
+        <f t="shared" ref="O42:O45" si="14">ROUND(L45*500*1.11,0)</f>
+        <v>555</v>
+      </c>
+      <c r="P45" s="11">
         <f t="shared" si="12"/>
-        <v>555</v>
-      </c>
-      <c r="P45" s="4">
+        <v>1110</v>
+      </c>
+      <c r="Q45" s="11">
         <f t="shared" si="13"/>
-        <v>1110</v>
-      </c>
-      <c r="Q45" s="4">
-        <f t="shared" si="14"/>
         <v>11100</v>
       </c>
       <c r="R45" s="12"/>
@@ -6036,21 +6447,21 @@
         <v>0</v>
       </c>
       <c r="W45" s="13"/>
-      <c r="X45" s="6">
+      <c r="X45" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y45" s="13"/>
-      <c r="Z45" s="6">
+      <c r="Z45" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA45" s="13"/>
-      <c r="AB45" s="6">
+      <c r="AB45" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC45" s="14"/>
+      <c r="AC45" s="38"/>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
     </row>
@@ -6058,76 +6469,91 @@
       <c r="A46" s="52">
         <v>44</v>
       </c>
-      <c r="B46" s="83"/>
-      <c r="C46" s="107" t="s">
+      <c r="B46" s="169"/>
+      <c r="C46" s="112" t="s">
         <v>203</v>
       </c>
-      <c r="D46" s="118" t="s">
-        <v>41</v>
-      </c>
-      <c r="E46" s="118" t="s">
+      <c r="D46" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="113" t="s">
         <v>204</v>
       </c>
-      <c r="F46" s="119" t="s">
+      <c r="F46" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="G46" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="H46" s="10"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="134">
+      <c r="G46" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="I46" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="K46" s="20">
+        <v>65</v>
+      </c>
+      <c r="L46" s="21">
         <v>1</v>
       </c>
-      <c r="M46" s="4">
-        <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="N46" s="4">
-        <f t="shared" si="11"/>
-        <v>22</v>
-      </c>
-      <c r="O46" s="4">
-        <f t="shared" si="12"/>
-        <v>555</v>
-      </c>
-      <c r="P46" s="4">
-        <f t="shared" si="13"/>
-        <v>1110</v>
-      </c>
-      <c r="Q46" s="4">
-        <f t="shared" si="14"/>
-        <v>11100</v>
-      </c>
-      <c r="R46" s="12"/>
-      <c r="S46" s="57"/>
-      <c r="T46" s="13">
+      <c r="M46" s="23">
+        <v>65</v>
+      </c>
+      <c r="N46" s="23">
+        <v>65</v>
+      </c>
+      <c r="O46" s="23">
+        <v>520</v>
+      </c>
+      <c r="P46" s="23">
+        <v>1050</v>
+      </c>
+      <c r="Q46" s="23">
+        <v>10200</v>
+      </c>
+      <c r="R46" s="173" t="s">
+        <v>307</v>
+      </c>
+      <c r="S46" s="158">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="T46" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U46" s="58"/>
-      <c r="V46" s="13">
+        <v>52.325000000000003</v>
+      </c>
+      <c r="U46" s="158">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="V46" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W46" s="13"/>
-      <c r="X46" s="6">
+        <v>52.325000000000003</v>
+      </c>
+      <c r="W46" s="25">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="X46" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="13"/>
-      <c r="Z46" s="6">
+        <v>301.59999999999997</v>
+      </c>
+      <c r="Y46" s="25">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Z46" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA46" s="13"/>
-      <c r="AB46" s="6">
+        <v>609</v>
+      </c>
+      <c r="AA46" s="25">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AB46" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC46" s="14"/>
+        <v>5916</v>
+      </c>
+      <c r="AC46" s="26"/>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
     </row>
@@ -6135,76 +6561,78 @@
       <c r="A47" s="52">
         <v>45</v>
       </c>
-      <c r="B47" s="83"/>
-      <c r="C47" s="120" t="s">
+      <c r="B47" s="168" t="s">
+        <v>206</v>
+      </c>
+      <c r="C47" s="188" t="s">
         <v>207</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="189" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="121" t="s">
+      <c r="E47" s="190" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="190" t="s">
         <v>208</v>
       </c>
-      <c r="F47" s="15" t="s">
+      <c r="G47" s="187" t="s">
         <v>209</v>
       </c>
-      <c r="G47" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="H47" s="30"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="10">
+      <c r="H47" s="183"/>
+      <c r="I47" s="181"/>
+      <c r="J47" s="182"/>
+      <c r="K47" s="174"/>
+      <c r="L47" s="191">
         <v>1</v>
       </c>
-      <c r="M47" s="4">
-        <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="N47" s="4">
-        <f t="shared" si="11"/>
-        <v>22</v>
-      </c>
-      <c r="O47" s="4">
-        <f t="shared" si="12"/>
-        <v>555</v>
-      </c>
-      <c r="P47" s="4">
-        <f t="shared" si="13"/>
-        <v>1110</v>
-      </c>
-      <c r="Q47" s="4">
-        <f t="shared" si="14"/>
-        <v>11100</v>
-      </c>
-      <c r="R47" s="12"/>
-      <c r="S47" s="57"/>
-      <c r="T47" s="13">
+      <c r="M47" s="174">
+        <f t="shared" ref="M47:M48" si="15">L47*10</f>
+        <v>10</v>
+      </c>
+      <c r="N47" s="174">
+        <f t="shared" ref="N47:N50" si="16">L47*20</f>
+        <v>20</v>
+      </c>
+      <c r="O47" s="174">
+        <f t="shared" ref="O47" si="17">L47*500</f>
+        <v>500</v>
+      </c>
+      <c r="P47" s="174">
+        <f t="shared" ref="P47" si="18">L47*1000</f>
+        <v>1000</v>
+      </c>
+      <c r="Q47" s="174">
+        <f t="shared" ref="Q47" si="19">L47*10000</f>
+        <v>10000</v>
+      </c>
+      <c r="R47" s="186"/>
+      <c r="S47" s="192"/>
+      <c r="T47" s="184">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U47" s="57"/>
-      <c r="V47" s="13">
+      <c r="U47" s="192"/>
+      <c r="V47" s="184">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W47" s="13"/>
-      <c r="X47" s="6">
+      <c r="W47" s="184"/>
+      <c r="X47" s="184">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y47" s="13"/>
-      <c r="Z47" s="6">
+      <c r="Y47" s="184"/>
+      <c r="Z47" s="184">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA47" s="13"/>
-      <c r="AB47" s="6">
+      <c r="AA47" s="184"/>
+      <c r="AB47" s="184">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC47" s="38"/>
+      <c r="AC47" s="198"/>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
     </row>
@@ -6212,76 +6640,92 @@
       <c r="A48" s="52">
         <v>46</v>
       </c>
-      <c r="B48" s="85"/>
-      <c r="C48" s="122" t="s">
+      <c r="B48" s="168"/>
+      <c r="C48" s="97" t="s">
         <v>210</v>
       </c>
-      <c r="D48" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" s="123" t="s">
+      <c r="D48" s="108" t="s">
         <v>211</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="E48" s="109" t="s">
+        <v>171</v>
+      </c>
+      <c r="F48" s="109" t="s">
         <v>212</v>
       </c>
-      <c r="G48" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="21">
+      <c r="G48" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="H48" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="I48" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K48" s="11">
+        <v>10</v>
+      </c>
+      <c r="L48" s="124">
         <v>1</v>
       </c>
-      <c r="M48" s="4">
-        <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="N48" s="4">
-        <f t="shared" si="11"/>
+      <c r="M48" s="11">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="N48" s="11">
         <v>22</v>
       </c>
-      <c r="O48" s="4">
-        <f t="shared" si="12"/>
-        <v>555</v>
-      </c>
-      <c r="P48" s="4">
-        <f t="shared" si="13"/>
-        <v>1110</v>
-      </c>
-      <c r="Q48" s="4">
-        <f t="shared" si="14"/>
-        <v>11100</v>
-      </c>
-      <c r="R48" s="157"/>
-      <c r="S48" s="182"/>
+      <c r="O48" s="11">
+        <v>520</v>
+      </c>
+      <c r="P48" s="11">
+        <v>1050</v>
+      </c>
+      <c r="Q48" s="11">
+        <v>10100</v>
+      </c>
+      <c r="R48" s="127" t="s">
+        <v>309</v>
+      </c>
+      <c r="S48" s="57">
+        <v>0.22</v>
+      </c>
       <c r="T48" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U48" s="182"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="U48" s="57">
+        <v>0.22</v>
+      </c>
       <c r="V48" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W48" s="25"/>
-      <c r="X48" s="6">
+        <v>4.84</v>
+      </c>
+      <c r="W48" s="13">
+        <v>0.19</v>
+      </c>
+      <c r="X48" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="25"/>
-      <c r="Z48" s="6">
+        <v>98.8</v>
+      </c>
+      <c r="Y48" s="13">
+        <v>0.19</v>
+      </c>
+      <c r="Z48" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA48" s="25"/>
-      <c r="AB48" s="6">
+        <v>199.5</v>
+      </c>
+      <c r="AA48" s="13">
+        <v>0.19</v>
+      </c>
+      <c r="AB48" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC48" s="26"/>
+        <v>1919</v>
+      </c>
+      <c r="AC48" s="14"/>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
     </row>
@@ -6289,370 +6733,282 @@
       <c r="A49" s="52">
         <v>47</v>
       </c>
-      <c r="B49" s="84" t="s">
+      <c r="B49" s="168"/>
+      <c r="C49" s="95" t="s">
         <v>213</v>
       </c>
-      <c r="C49" s="124" t="s">
+      <c r="D49" s="108" t="s">
         <v>214</v>
       </c>
-      <c r="D49" s="116" t="s">
-        <v>43</v>
-      </c>
-      <c r="E49" s="117" t="s">
-        <v>178</v>
-      </c>
-      <c r="F49" s="117" t="s">
+      <c r="E49" s="109" t="s">
+        <v>171</v>
+      </c>
+      <c r="F49" s="109" t="s">
         <v>215</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="135">
-        <v>1</v>
-      </c>
-      <c r="M49" s="4">
-        <f t="shared" ref="M49:M52" si="15">L49*10</f>
-        <v>10</v>
-      </c>
-      <c r="N49" s="4">
-        <f t="shared" ref="N49:N52" si="16">L49*20</f>
-        <v>20</v>
-      </c>
-      <c r="O49" s="4">
-        <f t="shared" ref="O49:O52" si="17">L49*500</f>
-        <v>500</v>
-      </c>
-      <c r="P49" s="4">
-        <f t="shared" ref="P49:P52" si="18">L49*1000</f>
-        <v>1000</v>
-      </c>
-      <c r="Q49" s="4">
-        <f t="shared" ref="Q49:Q52" si="19">L49*10000</f>
-        <v>10000</v>
-      </c>
-      <c r="R49" s="5"/>
-      <c r="S49" s="169"/>
+      <c r="H49" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K49" s="11">
+        <v>60</v>
+      </c>
+      <c r="L49" s="124">
+        <v>2</v>
+      </c>
+      <c r="M49" s="11">
+        <v>60</v>
+      </c>
+      <c r="N49" s="11">
+        <v>60</v>
+      </c>
+      <c r="O49" s="11">
+        <v>1050</v>
+      </c>
+      <c r="P49" s="11">
+        <v>2100</v>
+      </c>
+      <c r="Q49" s="11">
+        <v>20500</v>
+      </c>
+      <c r="R49" s="127" t="s">
+        <v>310</v>
+      </c>
+      <c r="S49" s="57">
+        <v>0.90700000000000003</v>
+      </c>
       <c r="T49" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U49" s="169"/>
+        <v>54.42</v>
+      </c>
+      <c r="U49" s="58">
+        <v>0.90700000000000003</v>
+      </c>
       <c r="V49" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W49" s="6"/>
-      <c r="X49" s="6">
+        <v>54.42</v>
+      </c>
+      <c r="W49" s="13">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="X49" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="6"/>
-      <c r="Z49" s="6">
+        <v>685.65</v>
+      </c>
+      <c r="Y49" s="13">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="Z49" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA49" s="6"/>
-      <c r="AB49" s="6">
+        <v>1371.3</v>
+      </c>
+      <c r="AA49" s="13">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="AB49" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC49" s="7"/>
+        <v>13386.5</v>
+      </c>
+      <c r="AC49" s="38"/>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
     </row>
     <row r="50" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="52">
+      <c r="A50" s="180">
         <v>48</v>
       </c>
-      <c r="B50" s="83"/>
-      <c r="C50" s="107" t="s">
+      <c r="B50" s="169"/>
+      <c r="C50" s="96" t="s">
         <v>217</v>
       </c>
-      <c r="D50" s="118" t="s">
+      <c r="D50" s="115" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="116" t="s">
         <v>218</v>
       </c>
-      <c r="E50" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="F50" s="119" t="s">
+      <c r="F50" s="116" t="s">
         <v>219</v>
       </c>
-      <c r="G50" s="9"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="136">
+      <c r="G50" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="H50" s="154" t="s">
+        <v>312</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="K50" s="149">
+        <v>20</v>
+      </c>
+      <c r="L50" s="125">
         <v>1</v>
       </c>
-      <c r="M50" s="11">
-        <f t="shared" si="15"/>
-        <v>10</v>
-      </c>
-      <c r="N50" s="11">
+      <c r="M50" s="23">
+        <v>20</v>
+      </c>
+      <c r="N50" s="23">
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
-      <c r="O50" s="11">
-        <f t="shared" si="17"/>
-        <v>500</v>
-      </c>
-      <c r="P50" s="11">
-        <f t="shared" si="18"/>
-        <v>1000</v>
-      </c>
-      <c r="Q50" s="11">
-        <f t="shared" si="19"/>
-        <v>10000</v>
-      </c>
-      <c r="R50" s="12"/>
-      <c r="S50" s="57"/>
-      <c r="T50" s="13">
+      <c r="O50" s="23">
+        <v>520</v>
+      </c>
+      <c r="P50" s="23">
+        <v>1160</v>
+      </c>
+      <c r="Q50" s="23">
+        <v>10200</v>
+      </c>
+      <c r="R50" s="155" t="s">
+        <v>15</v>
+      </c>
+      <c r="S50" s="156">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="T50" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U50" s="57"/>
-      <c r="V50" s="13">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="U50" s="157">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="V50" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W50" s="13"/>
-      <c r="X50" s="6">
+        <v>0.70199999999999996</v>
+      </c>
+      <c r="W50" s="25">
+        <v>2.7E-2</v>
+      </c>
+      <c r="X50" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="13"/>
-      <c r="Z50" s="6">
+        <v>14.04</v>
+      </c>
+      <c r="Y50" s="25">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="Z50" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA50" s="13"/>
-      <c r="AB50" s="6">
+        <v>29.58</v>
+      </c>
+      <c r="AA50" s="25">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="AB50" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC50" s="14"/>
+        <v>179.52</v>
+      </c>
+      <c r="AC50" s="26"/>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
     </row>
     <row r="51" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="52">
-        <v>49</v>
-      </c>
-      <c r="B51" s="83"/>
-      <c r="C51" s="102" t="s">
-        <v>220</v>
-      </c>
-      <c r="D51" s="118" t="s">
-        <v>221</v>
-      </c>
-      <c r="E51" s="119" t="s">
-        <v>178</v>
-      </c>
-      <c r="F51" s="119" t="s">
-        <v>222</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="136">
-        <v>2</v>
-      </c>
-      <c r="M51" s="11">
-        <f t="shared" si="15"/>
-        <v>20</v>
-      </c>
-      <c r="N51" s="11">
-        <f t="shared" si="16"/>
-        <v>40</v>
-      </c>
-      <c r="O51" s="11">
-        <f t="shared" si="17"/>
-        <v>1000</v>
-      </c>
-      <c r="P51" s="11">
-        <f t="shared" si="18"/>
-        <v>2000</v>
-      </c>
-      <c r="Q51" s="11">
-        <f t="shared" si="19"/>
-        <v>20000</v>
-      </c>
-      <c r="R51" s="12"/>
-      <c r="S51" s="57"/>
-      <c r="T51" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U51" s="58"/>
-      <c r="V51" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W51" s="13"/>
-      <c r="X51" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="13"/>
-      <c r="Z51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA51" s="13"/>
-      <c r="AB51" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC51" s="38"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="45"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="171" t="s">
+        <v>44</v>
+      </c>
+      <c r="M51" s="171"/>
+      <c r="N51" s="171"/>
+      <c r="O51" s="171"/>
+      <c r="P51" s="171"/>
+      <c r="Q51" s="171"/>
+      <c r="R51" s="171"/>
+      <c r="S51" s="171"/>
+      <c r="T51" s="49"/>
+      <c r="U51" s="49"/>
+      <c r="V51" s="41">
+        <f>SUM(V3:V49)</f>
+        <v>337.57299999999987</v>
+      </c>
+      <c r="W51" s="41"/>
+      <c r="X51" s="41">
+        <f>SUM(X3:X50)</f>
+        <v>5369.4264999999978</v>
+      </c>
+      <c r="Y51" s="41"/>
+      <c r="Z51" s="41">
+        <f>SUM(Z3:Z50)</f>
+        <v>9757.6049999999977</v>
+      </c>
+      <c r="AA51" s="41"/>
+      <c r="AB51" s="41">
+        <f>SUM(AB3:AB50)</f>
+        <v>75599.959999999992</v>
+      </c>
+      <c r="AC51" s="45"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
     </row>
-    <row r="52" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="52">
-        <v>50</v>
-      </c>
-      <c r="B52" s="85"/>
-      <c r="C52" s="103" t="s">
-        <v>224</v>
-      </c>
-      <c r="D52" s="125" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" s="126" t="s">
-        <v>225</v>
-      </c>
-      <c r="F52" s="126" t="s">
-        <v>226</v>
-      </c>
-      <c r="G52" s="20"/>
-      <c r="H52" s="170"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="163"/>
-      <c r="L52" s="137">
-        <v>1</v>
-      </c>
-      <c r="M52" s="23">
-        <f t="shared" si="15"/>
-        <v>10</v>
-      </c>
-      <c r="N52" s="23">
-        <f t="shared" si="16"/>
-        <v>20</v>
-      </c>
-      <c r="O52" s="23">
-        <f t="shared" si="17"/>
-        <v>500</v>
-      </c>
-      <c r="P52" s="23">
-        <f t="shared" si="18"/>
-        <v>1000</v>
-      </c>
-      <c r="Q52" s="23">
-        <f t="shared" si="19"/>
-        <v>10000</v>
-      </c>
-      <c r="R52" s="171"/>
-      <c r="S52" s="172"/>
-      <c r="T52" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U52" s="173"/>
-      <c r="V52" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W52" s="25"/>
-      <c r="X52" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="25"/>
-      <c r="Z52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA52" s="25"/>
-      <c r="AB52" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC52" s="26"/>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="H52" s="45"/>
+      <c r="I52" s="45"/>
+      <c r="J52" s="47"/>
+      <c r="K52" s="45"/>
+      <c r="L52" s="170" t="s">
+        <v>45</v>
+      </c>
+      <c r="M52" s="170"/>
+      <c r="N52" s="170"/>
+      <c r="O52" s="170"/>
+      <c r="P52" s="170"/>
+      <c r="Q52" s="170"/>
+      <c r="R52" s="170"/>
+      <c r="S52" s="170"/>
+      <c r="T52" s="41">
+        <f>SUM(T3:T49)</f>
+        <v>230.13835</v>
+      </c>
+      <c r="U52" s="46"/>
+      <c r="V52" s="48">
+        <f>V51/20</f>
+        <v>16.878649999999993</v>
+      </c>
+      <c r="W52" s="48"/>
+      <c r="X52" s="48">
+        <f>X51/500</f>
+        <v>10.738852999999995</v>
+      </c>
+      <c r="Y52" s="48"/>
+      <c r="Z52" s="48">
+        <f>Z51/1000</f>
+        <v>9.7576049999999981</v>
+      </c>
+      <c r="AA52" s="48"/>
+      <c r="AB52" s="48">
+        <f>AB51/10000</f>
+        <v>7.5599959999999991</v>
+      </c>
+      <c r="AC52" s="45"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
     </row>
-    <row r="53" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="86" t="s">
-        <v>45</v>
-      </c>
-      <c r="M53" s="86"/>
-      <c r="N53" s="86"/>
-      <c r="O53" s="86"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="86"/>
-      <c r="R53" s="86"/>
-      <c r="S53" s="86"/>
-      <c r="T53" s="49"/>
-      <c r="U53" s="49"/>
-      <c r="V53" s="41">
-        <f>SUM(V3:V51)</f>
-        <v>52.192699999999995</v>
-      </c>
-      <c r="W53" s="41"/>
-      <c r="X53" s="41"/>
-      <c r="Y53" s="41"/>
-      <c r="Z53" s="41"/>
-      <c r="AA53" s="41"/>
-      <c r="AB53" s="41"/>
-      <c r="AC53" s="45"/>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="T53">
+        <f>T52/10</f>
+        <v>23.013835</v>
+      </c>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="47"/>
-      <c r="K54" s="45"/>
-      <c r="L54" s="80" t="s">
-        <v>46</v>
-      </c>
-      <c r="M54" s="80"/>
-      <c r="N54" s="80"/>
-      <c r="O54" s="80"/>
-      <c r="P54" s="80"/>
-      <c r="Q54" s="80"/>
-      <c r="R54" s="80"/>
-      <c r="S54" s="80"/>
-      <c r="T54" s="41">
-        <f>SUM(T3:T51)</f>
-        <v>28.555699999999998</v>
-      </c>
-      <c r="U54" s="46"/>
-      <c r="V54" s="48">
-        <f>V53/5</f>
-        <v>10.43854</v>
-      </c>
-      <c r="W54" s="48"/>
-      <c r="X54" s="48"/>
-      <c r="Y54" s="48"/>
-      <c r="Z54" s="48"/>
-      <c r="AA54" s="48"/>
-      <c r="AB54" s="48"/>
-      <c r="AC54" s="45"/>
+      <c r="J54" s="42"/>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
     </row>
@@ -6663,13 +7019,10 @@
       <c r="AE55" s="8"/>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="J56" s="42"/>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="I57" s="43"/>
-      <c r="J57" s="43"/>
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
     </row>
@@ -6681,29 +7034,21 @@
       <c r="AD59" s="8"/>
       <c r="AE59" s="8"/>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="AD60" s="8"/>
-      <c r="AE60" s="8"/>
-    </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="AD61" s="8"/>
-      <c r="AE61" s="8"/>
-    </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="L54:S54"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="L52:S52"/>
     <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="L53:S53"/>
-    <mergeCell ref="B3:B12"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B23:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="L51:S51"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B22:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B39:B46"/>
   </mergeCells>
-  <conditionalFormatting sqref="AC47">
+  <conditionalFormatting sqref="AC45">
     <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
@@ -6717,7 +7062,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC41">
+  <conditionalFormatting sqref="AC39">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -6731,7 +7076,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC18">
+  <conditionalFormatting sqref="AC17">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -6745,7 +7090,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC13">
+  <conditionalFormatting sqref="AC12">
     <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
@@ -6773,7 +7118,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R45:R51">
+  <conditionalFormatting sqref="R43:R49">
     <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
@@ -6787,7 +7132,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R20:R22">
+  <conditionalFormatting sqref="R19:R21">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
@@ -6801,7 +7146,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R31:R35">
+  <conditionalFormatting sqref="R29:R33">
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -6815,7 +7160,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC51">
+  <conditionalFormatting sqref="AC49">
     <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
@@ -6829,57 +7174,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:Q52">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V3:AB52">
-    <cfRule type="dataBar" priority="45">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C84B8479-0C38-4E8A-A10C-CE0A75F3F79C}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L52">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L52">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T54:AB54">
+  <conditionalFormatting sqref="T52:AB52">
     <cfRule type="dataBar" priority="46">
       <dataBar>
         <cfvo type="min"/>
@@ -6893,8 +7188,58 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T3:T52">
-    <cfRule type="dataBar" priority="48">
+  <conditionalFormatting sqref="M3:Q50">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V3:AB50">
+    <cfRule type="dataBar" priority="60">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C84B8479-0C38-4E8A-A10C-CE0A75F3F79C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L50">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L50">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T3:T50">
+    <cfRule type="dataBar" priority="66">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6918,20 +7263,40 @@
     <hyperlink ref="R10" r:id="rId8"/>
     <hyperlink ref="R11" r:id="rId9"/>
     <hyperlink ref="R12" r:id="rId10"/>
-    <hyperlink ref="R13" r:id="rId11"/>
+    <hyperlink ref="R15" r:id="rId11"/>
     <hyperlink ref="R16" r:id="rId12"/>
     <hyperlink ref="R17" r:id="rId13"/>
     <hyperlink ref="R18" r:id="rId14"/>
-    <hyperlink ref="R19" r:id="rId15"/>
+    <hyperlink ref="R21" r:id="rId15"/>
     <hyperlink ref="R22" r:id="rId16"/>
     <hyperlink ref="R23" r:id="rId17"/>
     <hyperlink ref="R24" r:id="rId18"/>
     <hyperlink ref="R25" r:id="rId19"/>
-    <hyperlink ref="R26" r:id="rId20"/>
-    <hyperlink ref="R28" r:id="rId21"/>
+    <hyperlink ref="R27" r:id="rId20"/>
+    <hyperlink ref="R26" r:id="rId21"/>
+    <hyperlink ref="R29" r:id="rId22"/>
+    <hyperlink ref="R30" r:id="rId23"/>
+    <hyperlink ref="R31" r:id="rId24"/>
+    <hyperlink ref="R32" r:id="rId25"/>
+    <hyperlink ref="R33" r:id="rId26"/>
+    <hyperlink ref="R34" r:id="rId27"/>
+    <hyperlink ref="R35" r:id="rId28"/>
+    <hyperlink ref="R36" r:id="rId29"/>
+    <hyperlink ref="R37" r:id="rId30"/>
+    <hyperlink ref="R39" r:id="rId31"/>
+    <hyperlink ref="R40" r:id="rId32"/>
+    <hyperlink ref="R41" r:id="rId33"/>
+    <hyperlink ref="R44" r:id="rId34"/>
+    <hyperlink ref="R46" r:id="rId35"/>
+    <hyperlink ref="R48" r:id="rId36"/>
+    <hyperlink ref="R49" r:id="rId37"/>
+    <hyperlink ref="R50" r:id="rId38"/>
+    <hyperlink ref="R42" r:id="rId39"/>
+    <hyperlink ref="R43" r:id="rId40"/>
+    <hyperlink ref="R13" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId42"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -6946,7 +7311,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AC47</xm:sqref>
+          <xm:sqref>AC45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{301945FE-B701-4118-A9C3-5DA9DF529466}">
@@ -6959,7 +7324,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AC41</xm:sqref>
+          <xm:sqref>AC39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C4FABE8D-C538-4F8C-AF3D-D761B6945538}">
@@ -6972,7 +7337,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AC18</xm:sqref>
+          <xm:sqref>AC17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{95C28DBC-1CBC-4CC5-8B31-E70202137348}">
@@ -6985,7 +7350,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AC13</xm:sqref>
+          <xm:sqref>AC12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{D0D7514C-12FE-4A4F-8D11-1841726592C8}">
@@ -7011,7 +7376,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R45:R51</xm:sqref>
+          <xm:sqref>R43:R49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{F0B90621-6DA6-4516-A516-05C42ACBDF1D}">
@@ -7024,7 +7389,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R20:R22</xm:sqref>
+          <xm:sqref>R19:R21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{3534E561-107E-40A4-8165-E983FF420B68}">
@@ -7037,7 +7402,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R31:R35</xm:sqref>
+          <xm:sqref>R29:R33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{7D9785A5-B7CB-4186-8A59-C6DD0A9D39F0}">
@@ -7050,7 +7415,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AC51</xm:sqref>
+          <xm:sqref>AC49</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{23C19627-CC72-4F8E-BAD3-5ABFD29CE306}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFD6007B"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>T52:AB52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C84B8479-0C38-4E8A-A10C-CE0A75F3F79C}">
@@ -7063,20 +7441,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>V3:AB52</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23C19627-CC72-4F8E-BAD3-5ABFD29CE306}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFD6007B"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>T54:AB54</xm:sqref>
+          <xm:sqref>V3:AB50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{CC5A7198-6EFD-4BBD-B2B4-FEA92BA29842}">
@@ -7089,7 +7454,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>T3:T52</xm:sqref>
+          <xm:sqref>T3:T50</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
